--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -25,7 +25,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Requis!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Requis!$A$1:$L$65</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Tests!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$133</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$137</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,9 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="998">
-  <si>
-    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.3.0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1013">
+  <si>
+    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.4.0</t>
   </si>
   <si>
     <t xml:space="preserve">Spécification NCS/00/I/COMMON----/ES/010 Rev. A (13/10/2026) — relecture : Sébastien Kubasik — état au 28/10/2026</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (132 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (136 tests, tous OK).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 132/132 tests OK (Python 3.11 de référence,</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 136/136 tests OK (Python 3.11 de référence,</t>
   </si>
   <si>
     <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
@@ -314,22 +314,26 @@
     <t xml:space="preserve">core/signals.py, plotting/renderer.py</t>
   </si>
   <si>
+    <t xml:space="preserve">test_csv_reader.test_auto_types
+test_package_report.test_axes_are_gridded_and_lane_names_stay_inside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_2201 (1re ligne)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog signal type : float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal analogique : float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type Float, tracé continu, lu au plus proche échantillon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core/signals.py</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_csv_reader.test_auto_types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_2201 (1re ligne)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog signal type : float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal analogique : float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type Float, tracé continu, lu au plus proche échantillon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">core/signals.py</t>
   </si>
   <si>
     <t xml:space="preserve">n° 5</t>
@@ -706,7 +710,8 @@
     <t xml:space="preserve">system/environment.py, requirements.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_third_party_libraries_are_documented_and_pinned</t>
+    <t xml:space="preserve">test_architecture.test_third_party_libraries_are_documented_and_pinned
+test_architecture.test_windows_11_is_named_from_its_build_number</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_3005</t>
@@ -1047,13 +1052,14 @@
     <t xml:space="preserve">Plusieurs onglets pour différentes dispositions</t>
   </si>
   <si>
-    <t xml:space="preserve">Onglets créés depuis un modèle, renommables, fermables</t>
+    <t xml:space="preserve">Onglets créés depuis un modèle, renommables, fermables (croix du titre, clic molette, clic droit, Ctrl+W)</t>
   </si>
   <si>
     <t xml:space="preserve">gui/graph_area.py</t>
   </si>
   <si>
-    <t xml:space="preserve">test_gui.test_xy_tab_and_point_pick</t>
+    <t xml:space="preserve">test_gui.test_xy_tab_and_point_pick
+test_gui.test_tabs_close_with_their_cross</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5200</t>
@@ -1375,6 +1381,10 @@
     <t xml:space="preserve">En-tête + zone graphique (même rendu qu'à l'écran) + tableau des lectures</t>
   </si>
   <si>
+    <t xml:space="preserve">test_package_report.test_pdf_automatic_and_step_by_step
+test_package_report.test_report_page_layout_like_project_test_reports</t>
+  </si>
+  <si>
     <t xml:space="preserve">REQ_COMMON_KH_6002</t>
   </si>
   <si>
@@ -1513,6 +1523,9 @@
     <t xml:space="preserve">requirements.txt ; docs/DEPENDANCES.md ; ptbg/system/environment.py ; tools/audit_environnement.py</t>
   </si>
   <si>
+    <t xml:space="preserve">test_architecture.test_third_party_libraries_are_documented_and_pinned</t>
+  </si>
+  <si>
     <t xml:space="preserve">—</t>
   </si>
   <si>
@@ -2362,6 +2375,15 @@
     <t xml:space="preserve">5300</t>
   </si>
   <si>
+    <t xml:space="preserve">test_windows_11_is_named_from_its_build_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 3000 / 3004 : Python 3.11 annonce « Windows 10 » sous Windows 11 (noyau 10.0) ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000, 3004</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_every_requirement_is_traced</t>
   </si>
   <si>
@@ -2584,6 +2606,15 @@
     <t xml:space="preserve">5406</t>
   </si>
   <si>
+    <t xml:space="preserve">test_tabs_close_with_their_cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5106 : chaque onglet se ferme par la croix de son titre (ou clic molette,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5106</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_xy_tab_and_point_pick</t>
   </si>
   <si>
@@ -2714,6 +2745,24 @@
   </si>
   <si>
     <t xml:space="preserve">5401, 5403, 5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_axes_are_gridded_and_lane_names_stay_inside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5104 / 2200 : axes quadrillés (grille principale et sous-graduations en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2200, 5104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_report_page_layout_like_project_test_reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 6001 / 6005 : en-tête à chasse fixe, identification à gauche avec tous les</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6001, 6005</t>
   </si>
   <si>
     <t xml:space="preserve">test_pdf_automatic_and_step_by_step</t>
@@ -3887,8 +3936,8 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="n">
-        <f aca="false">COUNTA(Tests!$C$2:$C$133)</f>
-        <v>132</v>
+        <f aca="false">COUNTA(Tests!$C$2:$C$137)</f>
+        <v>136</v>
       </c>
       <c r="C15" s="13"/>
     </row>
@@ -4547,7 +4596,7 @@
       </c>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
         <v>20</v>
       </c>
@@ -4571,7 +4620,7 @@
         <v>90</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>5</v>
@@ -4602,7 +4651,7 @@
         <v>95</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>1</v>
@@ -4614,7 +4663,7 @@
         <v>5</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4622,23 +4671,23 @@
         <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>2</v>
@@ -4647,10 +4696,10 @@
         <v>6</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4658,23 +4707,23 @@
         <v>21</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>1</v>
@@ -4692,23 +4741,23 @@
         <v>21</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>5</v>
@@ -4720,7 +4769,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4728,23 +4777,23 @@
         <v>21</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>4</v>
@@ -4753,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" s="19"/>
     </row>
@@ -4762,23 +4811,23 @@
         <v>21</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="19" t="n">
         <v>2</v>
@@ -4796,23 +4845,23 @@
         <v>21</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I15" s="19" t="n">
         <v>1</v>
@@ -4830,25 +4879,25 @@
         <v>21</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I16" s="19" t="n">
         <v>2</v>
@@ -4857,10 +4906,10 @@
         <v>6</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4868,23 +4917,23 @@
         <v>21</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I17" s="19" t="n">
         <v>3</v>
@@ -4902,23 +4951,23 @@
         <v>21</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I18" s="19" t="n">
         <v>6</v>
@@ -4927,10 +4976,10 @@
         <v>6</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4938,23 +4987,23 @@
         <v>21</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I19" s="19" t="n">
         <v>3</v>
@@ -4972,23 +5021,23 @@
         <v>21</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I20" s="19" t="n">
         <v>1</v>
@@ -5006,23 +5055,23 @@
         <v>21</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I21" s="19" t="n">
         <v>1</v>
@@ -5031,10 +5080,10 @@
         <v>6</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5042,25 +5091,25 @@
         <v>22</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I22" s="19" t="n">
         <v>1</v>
@@ -5069,10 +5118,10 @@
         <v>8</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5080,25 +5129,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>1</v>
@@ -5107,10 +5156,10 @@
         <v>6</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5118,23 +5167,23 @@
         <v>22</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>1</v>
@@ -5152,23 +5201,23 @@
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>1</v>
@@ -5186,28 +5235,28 @@
         <v>22</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>5</v>
@@ -5222,23 +5271,23 @@
         <v>22</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I27" s="19" t="n">
         <v>1</v>
@@ -5256,23 +5305,23 @@
         <v>22</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I28" s="19" t="n">
         <v>1</v>
@@ -5290,23 +5339,23 @@
         <v>22</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I29" s="19" t="n">
         <v>1</v>
@@ -5324,23 +5373,23 @@
         <v>23</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I30" s="19" t="n">
         <v>2</v>
@@ -5349,10 +5398,10 @@
         <v>6</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L30" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5360,23 +5409,23 @@
         <v>23</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I31" s="19" t="n">
         <v>5</v>
@@ -5394,23 +5443,23 @@
         <v>23</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I32" s="19" t="n">
         <v>1</v>
@@ -5428,23 +5477,23 @@
         <v>23</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I33" s="19" t="n">
         <v>2</v>
@@ -5462,23 +5511,23 @@
         <v>23</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>1</v>
@@ -5496,23 +5545,23 @@
         <v>23</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I35" s="19" t="n">
         <v>12</v>
@@ -5521,10 +5570,10 @@
         <v>8</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5532,23 +5581,23 @@
         <v>23</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I36" s="19" t="n">
         <v>2</v>
@@ -5566,23 +5615,23 @@
         <v>23</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I37" s="19" t="n">
         <v>4</v>
@@ -5591,10 +5640,10 @@
         <v>6</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L37" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5602,23 +5651,23 @@
         <v>24</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I38" s="19" t="n">
         <v>1</v>
@@ -5636,23 +5685,23 @@
         <v>24</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I39" s="19" t="n">
         <v>1</v>
@@ -5670,23 +5719,23 @@
         <v>24</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I40" s="19" t="n">
         <v>1</v>
@@ -5704,23 +5753,23 @@
         <v>24</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I41" s="19" t="n">
         <v>1</v>
@@ -5738,23 +5787,23 @@
         <v>24</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>1</v>
@@ -5772,23 +5821,23 @@
         <v>24</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I43" s="19" t="n">
         <v>1</v>
@@ -5806,26 +5855,26 @@
         <v>24</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" s="19" t="s">
         <v>5</v>
@@ -5840,23 +5889,23 @@
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I45" s="19" t="n">
         <v>1</v>
@@ -5874,23 +5923,23 @@
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I46" s="19" t="n">
         <v>1</v>
@@ -5908,23 +5957,23 @@
         <v>25</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>2</v>
@@ -5933,10 +5982,10 @@
         <v>6</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5944,23 +5993,23 @@
         <v>25</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I48" s="19" t="n">
         <v>1</v>
@@ -5978,23 +6027,23 @@
         <v>26</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>2</v>
@@ -6012,23 +6061,23 @@
         <v>27</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I50" s="19" t="n">
         <v>1</v>
@@ -6046,23 +6095,23 @@
         <v>27</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I51" s="19" t="n">
         <v>2</v>
@@ -6071,10 +6120,10 @@
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,23 +6131,23 @@
         <v>27</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I52" s="19" t="n">
         <v>1</v>
@@ -6116,23 +6165,23 @@
         <v>27</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I53" s="19" t="n">
         <v>2</v>
@@ -6150,23 +6199,23 @@
         <v>27</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I54" s="19" t="n">
         <v>2</v>
@@ -6175,10 +6224,10 @@
         <v>6</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6186,23 +6235,23 @@
         <v>27</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I55" s="19" t="n">
         <v>1</v>
@@ -6220,23 +6269,23 @@
         <v>27</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I56" s="19" t="n">
         <v>2</v>
@@ -6254,23 +6303,23 @@
         <v>27</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I57" s="19" t="n">
         <v>2</v>
@@ -6279,10 +6328,10 @@
         <v>6</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6290,23 +6339,23 @@
         <v>27</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>2</v>
@@ -6315,10 +6364,10 @@
         <v>6</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6326,23 +6375,23 @@
         <v>28</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>1</v>
@@ -6351,10 +6400,10 @@
         <v>7</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6362,23 +6411,23 @@
         <v>29</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I60" s="19" t="n">
         <v>1</v>
@@ -6391,31 +6440,31 @@
       </c>
       <c r="L60" s="19"/>
     </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" s="19" t="s">
         <v>5</v>
@@ -6430,23 +6479,23 @@
         <v>29</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>1</v>
@@ -6464,23 +6513,23 @@
         <v>29</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="19" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>1</v>
@@ -6498,23 +6547,23 @@
         <v>29</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>1</v>
@@ -6532,35 +6581,35 @@
         <v>29</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="I65" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" s="19" t="s">
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -6612,129 +6661,129 @@
         <v>40</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -6767,22 +6816,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6790,16 +6839,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6808,16 +6857,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6826,16 +6875,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F4" s="21"/>
     </row>
@@ -6844,16 +6893,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F5" s="21"/>
     </row>
@@ -6862,16 +6911,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -6880,16 +6929,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -6898,16 +6947,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -6916,16 +6965,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -6934,16 +6983,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -6952,16 +7001,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -6970,16 +7019,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -6988,16 +7037,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7006,16 +7055,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7024,16 +7073,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F15" s="21"/>
     </row>
@@ -7042,16 +7091,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7060,16 +7109,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7078,16 +7127,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7096,16 +7145,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7139,33 +7188,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>79</v>
@@ -7174,18 +7223,18 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>128</v>
@@ -7194,18 +7243,18 @@
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>559</v>
-      </c>
       <c r="C4" s="19" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7214,18 +7263,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7234,18 +7283,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7254,18 +7303,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7274,18 +7323,18 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>49</v>
@@ -7294,18 +7343,18 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7314,18 +7363,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7334,18 +7383,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7354,18 +7403,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7374,18 +7423,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7394,18 +7443,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7414,18 +7463,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7434,18 +7483,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7454,18 +7503,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7474,18 +7523,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7494,18 +7543,18 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>486</v>
@@ -7514,38 +7563,38 @@
         <v>41</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>611</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>608</v>
-      </c>
       <c r="C20" s="19" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>67</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>269</v>
@@ -7554,18 +7603,18 @@
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>140</v>
@@ -7574,18 +7623,18 @@
         <v>17</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>119</v>
@@ -7594,38 +7643,38 @@
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>45</v>
@@ -7637,13 +7686,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D26" s="19" t="n">
         <v>140</v>
@@ -7652,18 +7701,18 @@
         <v>9</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D27" s="19" t="n">
         <v>92</v>
@@ -7672,18 +7721,18 @@
         <v>2</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>35</v>
@@ -7692,18 +7741,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>47</v>
@@ -7712,18 +7761,18 @@
         <v>4</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>59</v>
@@ -7732,18 +7781,18 @@
         <v>8</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>54</v>
@@ -7752,18 +7801,18 @@
         <v>7</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>198</v>
@@ -7772,18 +7821,18 @@
         <v>13</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>147</v>
@@ -7792,56 +7841,56 @@
         <v>8</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>653</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>650</v>
-      </c>
       <c r="C34" s="19" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>31</v>
@@ -7853,33 +7902,33 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>60</v>
@@ -7888,18 +7937,18 @@
         <v>9</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
+        <v>671</v>
+      </c>
+      <c r="B39" s="19" t="s">
         <v>668</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>665</v>
-      </c>
       <c r="C39" s="19" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>129</v>
@@ -7908,38 +7957,38 @@
         <v>10</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D40" s="19" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E40" s="19" t="n">
         <v>13</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>17</v>
@@ -7948,18 +7997,18 @@
         <v>1</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>105</v>
@@ -7968,18 +8017,18 @@
         <v>3</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>34</v>
@@ -7988,18 +8037,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>90</v>
@@ -8008,18 +8057,18 @@
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>101</v>
@@ -8028,18 +8077,18 @@
         <v>6</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>55</v>
@@ -8048,7 +8097,7 @@
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -8069,7 +8118,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -8081,2187 +8130,2255 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>761</v>
+        <v>736</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>579</v>
+        <v>770</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>769</v>
+        <v>582</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>770</v>
-      </c>
-      <c r="D31" s="19"/>
+        <v>773</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>774</v>
+      </c>
       <c r="E31" s="19" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>771</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>772</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>780</v>
-      </c>
-      <c r="D35" s="19"/>
+        <v>783</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>784</v>
+      </c>
       <c r="E35" s="19" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>782</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>783</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>684</v>
+        <v>787</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>784</v>
-      </c>
-      <c r="D37" s="19"/>
+        <v>788</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>789</v>
+      </c>
       <c r="E37" s="19" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>645</v>
+        <v>787</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>788</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>789</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>797</v>
+        <v>767</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>781</v>
+        <v>597</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>802</v>
-      </c>
-      <c r="D46" s="19"/>
+        <v>806</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>807</v>
+      </c>
       <c r="E46" s="19" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>804</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>805</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>806</v>
+        <v>766</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>820</v>
-      </c>
-      <c r="D53" s="19"/>
+        <v>823</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>824</v>
+      </c>
       <c r="E53" s="19" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>822</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>823</v>
-      </c>
+        <v>826</v>
+      </c>
+      <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>843</v>
+        <v>812</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>844</v>
+        <v>813</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>843</v>
+        <v>812</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>844</v>
+        <v>813</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>851</v>
-      </c>
-      <c r="D63" s="19"/>
+        <v>854</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>855</v>
+      </c>
       <c r="E63" s="19" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>860</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>861</v>
-      </c>
+        <v>864</v>
+      </c>
+      <c r="D67" s="19"/>
       <c r="E67" s="19" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>824</v>
+        <v>871</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>874</v>
+        <v>830</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>883</v>
-      </c>
-      <c r="D74" s="19"/>
+        <v>884</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>885</v>
+      </c>
       <c r="E74" s="19" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>773</v>
+        <v>892</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>779</v>
+        <v>897</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="D78" s="19"/>
       <c r="E78" s="19" t="s">
-        <v>779</v>
+        <v>897</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>891</v>
-      </c>
-      <c r="D79" s="19"/>
+        <v>899</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>900</v>
+      </c>
       <c r="E79" s="19" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>892</v>
-      </c>
-      <c r="D80" s="19"/>
+        <v>901</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>902</v>
+      </c>
       <c r="E80" s="19" t="s">
-        <v>882</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>882</v>
+        <v>785</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="D82" s="19"/>
       <c r="E82" s="19" t="s">
-        <v>579</v>
+        <v>785</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>896</v>
-      </c>
-      <c r="D83" s="19" t="s">
+        <v>906</v>
+      </c>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19" t="s">
         <v>897</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="D84" s="19"/>
       <c r="E84" s="19" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>899</v>
-      </c>
-      <c r="D85" s="19"/>
+        <v>908</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>909</v>
+      </c>
       <c r="E85" s="19" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>900</v>
-      </c>
-      <c r="D86" s="19" t="s">
-        <v>901</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="D86" s="19"/>
       <c r="E86" s="19" t="s">
-        <v>769</v>
+        <v>582</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>902</v>
-      </c>
-      <c r="D87" s="19"/>
+        <v>911</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>912</v>
+      </c>
       <c r="E87" s="19" t="s">
-        <v>769</v>
+        <v>897</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>903</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>904</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="D88" s="19"/>
       <c r="E88" s="19" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>906</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>907</v>
-      </c>
+        <v>914</v>
+      </c>
+      <c r="D89" s="19"/>
       <c r="E89" s="19" t="s">
-        <v>579</v>
+        <v>897</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>579</v>
+        <v>775</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>882</v>
+        <v>775</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>912</v>
-      </c>
-      <c r="D92" s="19"/>
+        <v>918</v>
+      </c>
+      <c r="D92" s="19" t="s">
+        <v>919</v>
+      </c>
       <c r="E92" s="19" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>882</v>
+        <v>582</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>916</v>
-      </c>
-      <c r="D94" s="19"/>
+        <v>923</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>924</v>
+      </c>
       <c r="E94" s="19" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>917</v>
-      </c>
-      <c r="D95" s="19" t="s">
-        <v>918</v>
-      </c>
+        <v>925</v>
+      </c>
+      <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>920</v>
-      </c>
-      <c r="D96" s="19" t="s">
-        <v>921</v>
-      </c>
+        <v>927</v>
+      </c>
+      <c r="D96" s="19"/>
       <c r="E96" s="19" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>882</v>
+        <v>934</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>827</v>
+        <v>934</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="D102" s="19" t="s">
-        <v>933</v>
-      </c>
+        <v>940</v>
+      </c>
+      <c r="D102" s="19"/>
       <c r="E102" s="19" t="s">
-        <v>645</v>
+        <v>928</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>645</v>
+        <v>833</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>942</v>
+        <v>851</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>945</v>
+        <v>648</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>842</v>
+        <v>897</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>913</v>
+        <v>648</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>913</v>
+        <v>957</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>959</v>
-      </c>
-      <c r="D113" s="19"/>
+        <v>965</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>966</v>
+      </c>
       <c r="E113" s="19" t="s">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>963</v>
-      </c>
-      <c r="D115" s="19"/>
+        <v>969</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>970</v>
+      </c>
       <c r="E115" s="19" t="s">
-        <v>960</v>
+        <v>859</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>966</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>967</v>
-      </c>
+        <v>974</v>
+      </c>
+      <c r="D117" s="19"/>
       <c r="E117" s="19" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>969</v>
-      </c>
-      <c r="D118" s="19"/>
+        <v>976</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>977</v>
+      </c>
       <c r="E118" s="19" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D119" s="19"/>
       <c r="E119" s="19" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>827</v>
+        <v>648</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>979</v>
-      </c>
-      <c r="D122" s="19" t="s">
-        <v>980</v>
-      </c>
+        <v>984</v>
+      </c>
+      <c r="D122" s="19"/>
       <c r="E122" s="19" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>982</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>983</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="D123" s="19"/>
       <c r="E123" s="19" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>842</v>
+        <v>993</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>988</v>
-      </c>
-      <c r="D126" s="19"/>
+        <v>994</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>995</v>
+      </c>
       <c r="E126" s="19" t="s">
-        <v>827</v>
+        <v>996</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>827</v>
+        <v>988</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>919</v>
+        <v>833</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>993</v>
-      </c>
-      <c r="D129" s="19"/>
+        <v>1001</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>1002</v>
+      </c>
       <c r="E129" s="19" t="s">
-        <v>973</v>
+        <v>851</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="D130" s="19"/>
       <c r="E130" s="19" t="s">
-        <v>973</v>
+        <v>833</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>995</v>
-      </c>
-      <c r="D131" s="19"/>
+        <v>1004</v>
+      </c>
+      <c r="D131" s="19" t="s">
+        <v>1005</v>
+      </c>
       <c r="E131" s="19" t="s">
-        <v>978</v>
+        <v>833</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>996</v>
-      </c>
-      <c r="D132" s="19"/>
+        <v>1006</v>
+      </c>
+      <c r="D132" s="19" t="s">
+        <v>1007</v>
+      </c>
       <c r="E132" s="19" t="s">
-        <v>973</v>
+        <v>934</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="D133" s="19"/>
       <c r="E133" s="19" t="s">
-        <v>973</v>
+        <v>988</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="19" t="s">
+        <v>985</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D134" s="19"/>
+      <c r="E134" s="19" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="19" t="s">
+        <v>985</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D135" s="19"/>
+      <c r="E135" s="19" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="19" t="s">
+        <v>985</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D136" s="19"/>
+      <c r="E136" s="19" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="19" t="s">
+        <v>985</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D137" s="19"/>
+      <c r="E137" s="19" t="s">
+        <v>988</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E133"/>
+  <autoFilter ref="A1:E137"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -25,7 +25,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Requis!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Requis!$A$1:$L$65</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Tests!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$137</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$138</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,9 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1013">
-  <si>
-    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.4.0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1018">
+  <si>
+    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.4.1</t>
   </si>
   <si>
     <t xml:space="preserve">Spécification NCS/00/I/COMMON----/ES/010 Rev. A (13/10/2026) — relecture : Sébastien Kubasik — état au 28/10/2026</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (136 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (137 tests, tous OK).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 136/136 tests OK (Python 3.11 de référence,</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 137/137 tests OK (Python 3.11 de référence,</t>
   </si>
   <si>
     <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
@@ -980,67 +980,71 @@
     <t xml:space="preserve">gui/info_windows.py</t>
   </si>
   <si>
+    <t xml:space="preserve">test_gui.test_information_windows_and_tree_toggle
+test_gui.test_markdown_tables_are_drawn_as_columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottom bar summarizing:UserDateActivity logTool version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barre inférieure : utilisateur, date, journal, version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barre d'état avec horloge, dernier message (clic = journal complet), version, avancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gui/status_bar.py, system/activity_log.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left area will contain the data tree viewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone gauche = arbre des données</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbre à gauche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIN.py, gui/tree_panel.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_5104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right area will be the main and wider section devoted to graphical analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone droite principale et plus large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone graphique à droite, seule à s'étirer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIN.py, gui/graph_area.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_5105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree area can be hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbre masquable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouton « Masquer », barre d'accès rapide, menu Affichage, F9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gui/app.py (toggle_tree)</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_gui.test_information_windows_and_tree_toggle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_5102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom bar summarizing:UserDateActivity logTool version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barre inférieure : utilisateur, date, journal, version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barre d'état avec horloge, dernier message (clic = journal complet), version, avancement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gui/status_bar.py, system/activity_log.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left area will contain the data tree viewer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone gauche = arbre des données</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbre à gauche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN.py, gui/tree_panel.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_5104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right area will be the main and wider section devoted to graphical analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone droite principale et plus large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone graphique à droite, seule à s'étirer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN.py, gui/graph_area.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_5105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree area can be hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbre masquable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouton « Masquer », barre d'accès rapide, menu Affichage, F9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gui/app.py (toggle_tree)</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5106</t>
@@ -2532,6 +2536,18 @@
   </si>
   <si>
     <t xml:space="preserve">test_gui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpViewerTests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_markdown_tables_are_drawn_as_columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5101 : dans l'aide et l'historique, un tableau Markdown est dessiné en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5101</t>
   </si>
   <si>
     <t xml:space="preserve">InterfaceTests</t>
@@ -3936,8 +3952,8 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="n">
-        <f aca="false">COUNTA(Tests!$C$2:$C$137)</f>
-        <v>136</v>
+        <f aca="false">COUNTA(Tests!$C$2:$C$138)</f>
+        <v>137</v>
       </c>
       <c r="C15" s="13"/>
     </row>
@@ -5704,7 +5720,7 @@
         <v>298</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="19" t="s">
         <v>5</v>
@@ -5837,7 +5853,7 @@
         <v>318</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="I43" s="19" t="n">
         <v>1</v>
@@ -5855,23 +5871,23 @@
         <v>24</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I44" s="19" t="n">
         <v>2</v>
@@ -5889,23 +5905,23 @@
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I45" s="19" t="n">
         <v>1</v>
@@ -5923,23 +5939,23 @@
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I46" s="19" t="n">
         <v>1</v>
@@ -5957,23 +5973,23 @@
         <v>25</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>2</v>
@@ -5982,10 +5998,10 @@
         <v>6</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5993,23 +6009,23 @@
         <v>25</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I48" s="19" t="n">
         <v>1</v>
@@ -6027,23 +6043,23 @@
         <v>26</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>2</v>
@@ -6061,23 +6077,23 @@
         <v>27</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I50" s="19" t="n">
         <v>1</v>
@@ -6095,23 +6111,23 @@
         <v>27</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I51" s="19" t="n">
         <v>2</v>
@@ -6120,10 +6136,10 @@
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6131,23 +6147,23 @@
         <v>27</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I52" s="19" t="n">
         <v>1</v>
@@ -6165,23 +6181,23 @@
         <v>27</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I53" s="19" t="n">
         <v>2</v>
@@ -6199,23 +6215,23 @@
         <v>27</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I54" s="19" t="n">
         <v>2</v>
@@ -6224,10 +6240,10 @@
         <v>6</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6235,23 +6251,23 @@
         <v>27</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I55" s="19" t="n">
         <v>1</v>
@@ -6269,23 +6285,23 @@
         <v>27</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I56" s="19" t="n">
         <v>2</v>
@@ -6303,23 +6319,23 @@
         <v>27</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I57" s="19" t="n">
         <v>2</v>
@@ -6328,10 +6344,10 @@
         <v>6</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6339,23 +6355,23 @@
         <v>27</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>2</v>
@@ -6364,10 +6380,10 @@
         <v>6</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6375,23 +6391,23 @@
         <v>28</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>1</v>
@@ -6400,10 +6416,10 @@
         <v>7</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6411,23 +6427,23 @@
         <v>29</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I60" s="19" t="n">
         <v>1</v>
@@ -6445,23 +6461,23 @@
         <v>29</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I61" s="19" t="n">
         <v>2</v>
@@ -6479,23 +6495,23 @@
         <v>29</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>1</v>
@@ -6513,23 +6529,23 @@
         <v>29</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>1</v>
@@ -6547,23 +6563,23 @@
         <v>29</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>1</v>
@@ -6581,23 +6597,23 @@
         <v>29</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>2</v>
@@ -6606,10 +6622,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -6661,25 +6677,25 @@
         <v>40</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6687,19 +6703,19 @@
         <v>137</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
@@ -6713,22 +6729,22 @@
         <v>179</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>187</v>
@@ -6739,19 +6755,19 @@
         <v>188</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
@@ -6765,25 +6781,25 @@
         <v>209</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -6816,22 +6832,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6839,16 +6855,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6857,16 +6873,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6875,13 +6891,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>193</v>
@@ -6893,13 +6909,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>220</v>
@@ -6911,16 +6927,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -6929,16 +6945,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -6947,16 +6963,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -6965,16 +6981,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -6983,16 +6999,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -7001,16 +7017,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7019,16 +7035,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -7037,16 +7053,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7055,16 +7071,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7073,13 +7089,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>122</v>
@@ -7091,16 +7107,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7109,16 +7125,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7127,16 +7143,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7145,16 +7161,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7188,33 +7204,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>79</v>
@@ -7223,18 +7239,18 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>128</v>
@@ -7243,18 +7259,18 @@
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7263,18 +7279,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7283,18 +7299,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7303,18 +7319,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7323,18 +7339,18 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>49</v>
@@ -7343,18 +7359,18 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7363,18 +7379,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7383,18 +7399,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7403,18 +7419,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7423,18 +7439,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7443,18 +7459,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7463,18 +7479,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7483,18 +7499,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7503,18 +7519,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7523,18 +7539,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7543,18 +7559,18 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>486</v>
@@ -7563,18 +7579,18 @@
         <v>41</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D20" s="19" t="n">
         <v>711</v>
@@ -7583,18 +7599,18 @@
         <v>67</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>269</v>
@@ -7603,18 +7619,18 @@
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>140</v>
@@ -7623,18 +7639,18 @@
         <v>17</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>119</v>
@@ -7643,18 +7659,18 @@
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D24" s="19" t="n">
         <v>128</v>
@@ -7663,18 +7679,18 @@
         <v>14</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>45</v>
@@ -7686,33 +7702,33 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D27" s="19" t="n">
         <v>92</v>
@@ -7721,18 +7737,18 @@
         <v>2</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>35</v>
@@ -7741,18 +7757,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>47</v>
@@ -7761,18 +7777,18 @@
         <v>4</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>59</v>
@@ -7781,18 +7797,18 @@
         <v>8</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>54</v>
@@ -7801,18 +7817,18 @@
         <v>7</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>198</v>
@@ -7821,18 +7837,18 @@
         <v>13</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>147</v>
@@ -7841,18 +7857,18 @@
         <v>8</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D34" s="19" t="n">
         <v>473</v>
@@ -7861,18 +7877,18 @@
         <v>29</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D35" s="19" t="n">
         <v>43</v>
@@ -7884,13 +7900,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>31</v>
@@ -7902,13 +7918,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D37" s="19" t="n">
         <v>187</v>
@@ -7917,18 +7933,18 @@
         <v>7</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>60</v>
@@ -7937,18 +7953,18 @@
         <v>9</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>129</v>
@@ -7957,18 +7973,18 @@
         <v>10</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D40" s="19" t="n">
         <v>183</v>
@@ -7977,18 +7993,18 @@
         <v>13</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>17</v>
@@ -7997,7 +8013,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8008,7 +8024,7 @@
         <v>201</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>105</v>
@@ -8017,18 +8033,18 @@
         <v>3</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>34</v>
@@ -8037,18 +8053,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>90</v>
@@ -8057,18 +8073,18 @@
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>101</v>
@@ -8077,18 +8093,18 @@
         <v>6</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>55</v>
@@ -8097,7 +8113,7 @@
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -8118,7 +8134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -8130,1032 +8146,1032 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>707</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>708</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>706</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>707</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B50" s="19" t="s">
+        <v>814</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>815</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="19" t="s">
         <v>813</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>815</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
-        <v>812</v>
-      </c>
       <c r="B51" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B53" s="19" t="s">
+        <v>818</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="19" t="s">
         <v>813</v>
       </c>
-      <c r="C53" s="19" t="s">
-        <v>823</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>824</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
-        <v>812</v>
-      </c>
       <c r="B54" s="19" t="s">
+        <v>818</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>828</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="s">
         <v>813</v>
       </c>
-      <c r="C54" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
-        <v>812</v>
-      </c>
       <c r="B55" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>828</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>829</v>
-      </c>
+        <v>831</v>
+      </c>
+      <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>852</v>
+        <v>813</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>853</v>
+        <v>818</v>
       </c>
       <c r="C63" s="19" t="s">
         <v>854</v>
@@ -9169,227 +9185,227 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>860</v>
-      </c>
-      <c r="D65" s="19"/>
+        <v>862</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>863</v>
+      </c>
       <c r="E65" s="19" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>861</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>862</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="D66" s="19"/>
       <c r="E66" s="19" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>864</v>
-      </c>
-      <c r="D67" s="19"/>
+        <v>866</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>867</v>
+      </c>
       <c r="E67" s="19" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>866</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>867</v>
-      </c>
+        <v>869</v>
+      </c>
+      <c r="D68" s="19"/>
       <c r="E68" s="19" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>830</v>
+        <v>880</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>880</v>
+        <v>835</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>893</v>
+        <v>857</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>894</v>
+        <v>877</v>
       </c>
       <c r="C77" s="19" t="s">
         <v>895</v>
@@ -9403,944 +9419,946 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>898</v>
-      </c>
-      <c r="D78" s="19"/>
+        <v>900</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>901</v>
+      </c>
       <c r="E78" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>899</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>900</v>
-      </c>
+        <v>903</v>
+      </c>
+      <c r="D79" s="19"/>
       <c r="E79" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D80" s="19" t="s">
+        <v>905</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>902</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>905</v>
-      </c>
-      <c r="D82" s="19"/>
+        <v>908</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>909</v>
+      </c>
       <c r="E82" s="19" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D83" s="19"/>
       <c r="E83" s="19" t="s">
-        <v>897</v>
+        <v>786</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="D84" s="19"/>
       <c r="E84" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>908</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>909</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="D85" s="19"/>
       <c r="E85" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>910</v>
-      </c>
-      <c r="D86" s="19"/>
+        <v>913</v>
+      </c>
+      <c r="D86" s="19" t="s">
+        <v>914</v>
+      </c>
       <c r="E86" s="19" t="s">
-        <v>582</v>
+        <v>902</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>911</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>912</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="D87" s="19"/>
       <c r="E87" s="19" t="s">
-        <v>897</v>
+        <v>583</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>913</v>
-      </c>
-      <c r="D88" s="19"/>
+        <v>916</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>917</v>
+      </c>
       <c r="E88" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D89" s="19"/>
       <c r="E89" s="19" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>915</v>
-      </c>
-      <c r="D90" s="19" t="s">
-        <v>916</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="D90" s="19"/>
       <c r="E90" s="19" t="s">
-        <v>775</v>
+        <v>902</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>917</v>
-      </c>
-      <c r="D91" s="19"/>
+        <v>920</v>
+      </c>
+      <c r="D91" s="19" t="s">
+        <v>921</v>
+      </c>
       <c r="E91" s="19" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>918</v>
-      </c>
-      <c r="D92" s="19" t="s">
-        <v>919</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>920</v>
+        <v>776</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>582</v>
+        <v>925</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>925</v>
-      </c>
-      <c r="D95" s="19"/>
+        <v>928</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>929</v>
+      </c>
       <c r="E95" s="19" t="s">
-        <v>897</v>
+        <v>583</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>926</v>
+        <v>899</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D96" s="19"/>
       <c r="E96" s="19" t="s">
-        <v>928</v>
+        <v>902</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>929</v>
-      </c>
-      <c r="D97" s="19" t="s">
-        <v>930</v>
-      </c>
+        <v>932</v>
+      </c>
+      <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>897</v>
+        <v>933</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C98" s="19" t="s">
+        <v>934</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>935</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="19" t="s">
+        <v>898</v>
+      </c>
+      <c r="B99" s="19" t="s">
         <v>931</v>
       </c>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="19" t="s">
-        <v>893</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>926</v>
-      </c>
       <c r="C99" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="D99" s="19" t="s">
-        <v>933</v>
-      </c>
+        <v>936</v>
+      </c>
+      <c r="D99" s="19"/>
       <c r="E99" s="19" t="s">
-        <v>934</v>
+        <v>902</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>940</v>
-      </c>
-      <c r="D102" s="19"/>
+        <v>942</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>943</v>
+      </c>
       <c r="E102" s="19" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>941</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>942</v>
-      </c>
+        <v>945</v>
+      </c>
+      <c r="D103" s="19"/>
       <c r="E103" s="19" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>648</v>
+        <v>856</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>897</v>
+        <v>649</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>648</v>
+        <v>902</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>953</v>
+        <v>898</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>954</v>
+        <v>931</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>957</v>
+        <v>649</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>851</v>
+        <v>965</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>928</v>
+        <v>856</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>859</v>
+        <v>962</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>974</v>
-      </c>
-      <c r="D117" s="19"/>
+        <v>976</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>977</v>
+      </c>
       <c r="E117" s="19" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>976</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>977</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="D118" s="19"/>
       <c r="E118" s="19" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>978</v>
-      </c>
-      <c r="D119" s="19"/>
+        <v>981</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>982</v>
+      </c>
       <c r="E119" s="19" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>979</v>
-      </c>
-      <c r="D120" s="19" t="s">
+        <v>983</v>
+      </c>
+      <c r="D120" s="19"/>
+      <c r="E120" s="19" t="s">
         <v>980</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>984</v>
-      </c>
-      <c r="D122" s="19"/>
+        <v>986</v>
+      </c>
+      <c r="D122" s="19" t="s">
+        <v>987</v>
+      </c>
       <c r="E122" s="19" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>985</v>
+        <v>958</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>986</v>
+        <v>959</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D123" s="19"/>
       <c r="E123" s="19" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>989</v>
-      </c>
-      <c r="D124" s="19" t="s">
-        <v>990</v>
-      </c>
+        <v>992</v>
+      </c>
+      <c r="D124" s="19"/>
       <c r="E124" s="19" t="s">
-        <v>833</v>
+        <v>993</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>993</v>
+        <v>838</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>988</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>833</v>
+        <v>993</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D130" s="19"/>
+        <v>1006</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>1007</v>
+      </c>
       <c r="E130" s="19" t="s">
-        <v>833</v>
+        <v>856</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D131" s="19" t="s">
-        <v>1005</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="D131" s="19"/>
       <c r="E131" s="19" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>934</v>
+        <v>838</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D133" s="19"/>
+        <v>1011</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>1012</v>
+      </c>
       <c r="E133" s="19" t="s">
-        <v>988</v>
+        <v>939</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D134" s="19"/>
       <c r="E134" s="19" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D135" s="19"/>
       <c r="E135" s="19" t="s">
@@ -10349,36 +10367,51 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="D136" s="19"/>
       <c r="E136" s="19" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="D137" s="19"/>
       <c r="E137" s="19" t="s">
-        <v>988</v>
+        <v>993</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>991</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D138" s="19"/>
+      <c r="E138" s="19" t="s">
+        <v>993</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E137"/>
+  <autoFilter ref="A1:E138"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -25,7 +25,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Requis!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Requis!$A$1:$L$65</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Tests!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$138</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$141</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,9 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1018">
-  <si>
-    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.4.1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1028">
+  <si>
+    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.5.0</t>
   </si>
   <si>
     <t xml:space="preserve">Spécification NCS/00/I/COMMON----/ES/010 Rev. A (13/10/2026) — relecture : Sébastien Kubasik — état au 28/10/2026</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (137 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (140 tests, tous OK).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 137/137 tests OK (Python 3.11 de référence,</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 140/140 tests OK (Python 3.11 de référence,</t>
   </si>
   <si>
     <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
@@ -809,7 +809,8 @@
 test_wrong_phasing_detected
 test_robustesse.test_isolated_aberrant_timestamp_is_one_error_not_a_fake_gap
 test_aberrant_timestamp_stays_visible_unless_hidden
-test_nan_and_inf_are_missing_values_not_text</t>
+test_nan_and_inf_are_missing_values_not_text
+test_gui.test_diagnostic_window_is_readable</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_4102</t>
@@ -1063,7 +1064,9 @@
   </si>
   <si>
     <t xml:space="preserve">test_gui.test_xy_tab_and_point_pick
-test_gui.test_tabs_close_with_their_cross</t>
+test_gui.test_tabs_close_with_their_cross
+test_gui.test_reset_view_returns_to_full_duration
+test_gui.test_legend_can_be_moved_hidden_and_picks_curves</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5200</t>
@@ -1386,72 +1389,77 @@
   </si>
   <si>
     <t xml:space="preserve">test_package_report.test_pdf_automatic_and_step_by_step
+test_package_report.test_report_page_layout_like_project_test_reports
+test_gui.test_legend_can_be_moved_hidden_and_picks_curves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_6002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report, can be generated automatically or step by step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatique ou pas à pas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu Rapport : automatique / pas à pas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gui/app.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_gui.test_reports_and_project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_6003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic Report consist into a single edition of active graphical area to pdf file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatique = édition unique de l'onglet actif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une page de l'onglet actif + traçabilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gui/app.py (automatic_report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_6004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual step by step report generation consist into a sequential generation on order depending of graphical active tab. Permitting to push global view, and customize analysis, cursor, X/Y cloud…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas à pas = génération séquentielle selon l'onglet actif (vue globale, analyse, curseurs, nuage X/Y…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captures figées successives (zoom, curseurs, X/Y, condition, commentaire), ordonnables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gui/app.py (add_report_page), gui/dialogs/report_dialogs.py (PagesWindow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ_COMMON_KH_6005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header shall contain following details:Tool VersionIssuerDateSource File(s)Project Name &amp; UnitProject file reference or Hash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En-tête : version, émetteur, date, fichiers sources, projet et unité, référence ou empreinte du projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tous ces champs ; SHA-256 des sources et du fichier projet ; annexe de traçabilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">report/pdf_report.py (build_header)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_package_report.test_pdf_automatic_and_step_by_step
 test_package_report.test_report_page_layout_like_project_test_reports</t>
   </si>
   <si>
-    <t xml:space="preserve">REQ_COMMON_KH_6002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report, can be generated automatically or step by step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatique ou pas à pas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu Rapport : automatique / pas à pas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gui/app.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_gui.test_reports_and_project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_6003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic Report consist into a single edition of active graphical area to pdf file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatique = édition unique de l'onglet actif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une page de l'onglet actif + traçabilité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gui/app.py (automatic_report)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_6004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual step by step report generation consist into a sequential generation on order depending of graphical active tab. Permitting to push global view, and customize analysis, cursor, X/Y cloud…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pas à pas = génération séquentielle selon l'onglet actif (vue globale, analyse, curseurs, nuage X/Y…)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Captures figées successives (zoom, curseurs, X/Y, condition, commentaire), ordonnables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gui/app.py (add_report_page), gui/dialogs/report_dialogs.py (PagesWindow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ_COMMON_KH_6005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header shall contain following details:Tool VersionIssuerDateSource File(s)Project Name &amp; UnitProject file reference or Hash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En-tête : version, émetteur, date, fichiers sources, projet et unité, référence ou empreinte du projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tous ces champs ; SHA-256 des sources et du fichier projet ; annexe de traçabilité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report/pdf_report.py (build_header)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implémenté — interprétation à valider (fichier projet .ptbg.json)</t>
   </si>
   <si>
@@ -2620,6 +2628,33 @@
   </si>
   <si>
     <t xml:space="preserve">5406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_reset_view_returns_to_full_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5106 / 5405 : après un zoom et un déplacement vertical, « Vue d'origine »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5106, 5405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_diagnostic_window_is_readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 4101 / 2300 : la fenêtre Diagnostic se lit sans balisage : gravités en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2300, 4101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_legend_can_be_moved_hidden_and_picks_curves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5106 / 6001 : la légende se glisse à la souris et garde sa place (redessin,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5106, 6001</t>
   </si>
   <si>
     <t xml:space="preserve">test_tabs_close_with_their_cross</t>
@@ -3952,8 +3987,8 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="n">
-        <f aca="false">COUNTA(Tests!$C$2:$C$138)</f>
-        <v>137</v>
+        <f aca="false">COUNTA(Tests!$C$2:$C$141)</f>
+        <v>140</v>
       </c>
       <c r="C15" s="13"/>
     </row>
@@ -5420,7 +5455,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
         <v>23</v>
       </c>
@@ -5444,7 +5479,7 @@
         <v>246</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="19" t="s">
         <v>5</v>
@@ -5866,7 +5901,7 @@
       </c>
       <c r="L43" s="19"/>
     </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -5890,7 +5925,7 @@
         <v>325</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" s="19" t="s">
         <v>5</v>
@@ -6456,7 +6491,7 @@
       </c>
       <c r="L60" s="19"/>
     </row>
-    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
         <v>29</v>
       </c>
@@ -6480,7 +6515,7 @@
         <v>430</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61" s="19" t="s">
         <v>5</v>
@@ -6613,7 +6648,7 @@
         <v>451</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>2</v>
@@ -6622,10 +6657,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -6677,25 +6712,25 @@
         <v>40</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6703,19 +6738,19 @@
         <v>137</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
@@ -6729,22 +6764,22 @@
         <v>179</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>187</v>
@@ -6755,19 +6790,19 @@
         <v>188</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
@@ -6781,25 +6816,25 @@
         <v>209</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -6832,22 +6867,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6855,16 +6890,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6873,16 +6908,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6891,13 +6926,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>193</v>
@@ -6909,13 +6944,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>220</v>
@@ -6927,16 +6962,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -6945,16 +6980,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -6963,16 +6998,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -6981,16 +7016,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -6999,16 +7034,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -7017,16 +7052,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7035,16 +7070,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -7053,16 +7088,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7071,16 +7106,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7089,13 +7124,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>122</v>
@@ -7107,16 +7142,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7125,16 +7160,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7143,16 +7178,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7161,16 +7196,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7204,33 +7239,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>79</v>
@@ -7239,38 +7274,38 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D3" s="19" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E3" s="19" t="n">
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7279,18 +7314,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7299,18 +7334,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7319,18 +7354,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7339,38 +7374,38 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7379,18 +7414,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7399,18 +7434,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7419,18 +7454,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7439,18 +7474,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7459,18 +7494,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7479,18 +7514,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7499,18 +7534,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7519,18 +7554,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7539,18 +7574,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7559,58 +7594,58 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>486</v>
+        <v>553</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>269</v>
@@ -7619,18 +7654,18 @@
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>140</v>
@@ -7639,18 +7674,18 @@
         <v>17</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>119</v>
@@ -7659,18 +7694,18 @@
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D24" s="19" t="n">
         <v>128</v>
@@ -7679,18 +7714,18 @@
         <v>14</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>45</v>
@@ -7702,53 +7737,53 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>35</v>
@@ -7757,18 +7792,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>47</v>
@@ -7777,18 +7812,18 @@
         <v>4</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>59</v>
@@ -7797,18 +7832,18 @@
         <v>8</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>54</v>
@@ -7817,18 +7852,18 @@
         <v>7</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>198</v>
@@ -7837,18 +7872,18 @@
         <v>13</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>147</v>
@@ -7857,38 +7892,38 @@
         <v>8</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E34" s="19" t="n">
         <v>29</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D35" s="19" t="n">
         <v>43</v>
@@ -7900,13 +7935,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>31</v>
@@ -7918,13 +7953,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D37" s="19" t="n">
         <v>187</v>
@@ -7933,18 +7968,18 @@
         <v>7</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>60</v>
@@ -7953,18 +7988,18 @@
         <v>9</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>129</v>
@@ -7973,18 +8008,18 @@
         <v>10</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D40" s="19" t="n">
         <v>183</v>
@@ -7993,18 +8028,18 @@
         <v>13</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>17</v>
@@ -8013,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8024,7 +8059,7 @@
         <v>201</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>105</v>
@@ -8033,18 +8068,18 @@
         <v>3</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>34</v>
@@ -8053,18 +8088,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>90</v>
@@ -8073,18 +8108,18 @@
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>101</v>
@@ -8093,18 +8128,18 @@
         <v>6</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>55</v>
@@ -8113,7 +8148,7 @@
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -8134,7 +8169,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -8146,1181 +8181,1181 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>708</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>707</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>708</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="B64" s="19" t="s">
+        <v>819</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>858</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="D64" s="19" t="s">
         <v>859</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="E64" s="19" t="s">
         <v>860</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>858</v>
+        <v>819</v>
       </c>
       <c r="C65" s="19" t="s">
+        <v>861</v>
+      </c>
+      <c r="D65" s="19" t="s">
         <v>862</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="E65" s="19" t="s">
         <v>863</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>857</v>
+        <v>814</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>858</v>
+        <v>819</v>
       </c>
       <c r="C66" s="19" t="s">
+        <v>864</v>
+      </c>
+      <c r="D66" s="19" t="s">
         <v>865</v>
       </c>
-      <c r="D66" s="19"/>
       <c r="E66" s="19" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>869</v>
-      </c>
-      <c r="D68" s="19"/>
+        <v>872</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>873</v>
+      </c>
       <c r="E68" s="19" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>871</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>872</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="D69" s="19"/>
       <c r="E69" s="19" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>878</v>
-      </c>
-      <c r="D71" s="19" t="s">
         <v>879</v>
       </c>
+      <c r="D71" s="19"/>
       <c r="E71" s="19" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>881</v>
@@ -9329,654 +9364,654 @@
         <v>882</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>835</v>
+        <v>883</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>891</v>
+        <v>836</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>898</v>
+        <v>867</v>
       </c>
       <c r="B78" s="19" t="s">
+        <v>887</v>
+      </c>
+      <c r="C78" s="19" t="s">
         <v>899</v>
       </c>
-      <c r="C78" s="19" t="s">
+      <c r="D78" s="19" t="s">
         <v>900</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="E78" s="19" t="s">
         <v>901</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>898</v>
+        <v>867</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="C79" s="19" t="s">
+        <v>902</v>
+      </c>
+      <c r="D79" s="19" t="s">
         <v>903</v>
       </c>
-      <c r="D79" s="19"/>
       <c r="E79" s="19" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>898</v>
+        <v>867</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>780</v>
+        <v>912</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>908</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>909</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="D82" s="19"/>
       <c r="E82" s="19" t="s">
-        <v>786</v>
+        <v>912</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>910</v>
-      </c>
-      <c r="D83" s="19"/>
+        <v>914</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>915</v>
+      </c>
       <c r="E83" s="19" t="s">
-        <v>786</v>
+        <v>912</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>911</v>
-      </c>
-      <c r="D84" s="19"/>
+        <v>916</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>917</v>
+      </c>
       <c r="E84" s="19" t="s">
-        <v>902</v>
+        <v>781</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>912</v>
-      </c>
-      <c r="D85" s="19"/>
+        <v>918</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>919</v>
+      </c>
       <c r="E85" s="19" t="s">
-        <v>902</v>
+        <v>787</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>913</v>
-      </c>
-      <c r="D86" s="19" t="s">
-        <v>914</v>
-      </c>
+        <v>920</v>
+      </c>
+      <c r="D86" s="19"/>
       <c r="E86" s="19" t="s">
-        <v>902</v>
+        <v>787</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="D87" s="19"/>
       <c r="E87" s="19" t="s">
-        <v>583</v>
+        <v>912</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>916</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>917</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="D88" s="19"/>
       <c r="E88" s="19" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>918</v>
-      </c>
-      <c r="D89" s="19"/>
+        <v>923</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>924</v>
+      </c>
       <c r="E89" s="19" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="19" t="s">
-        <v>902</v>
+        <v>584</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>776</v>
+        <v>912</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>776</v>
+        <v>912</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>923</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>924</v>
-      </c>
+        <v>929</v>
+      </c>
+      <c r="D93" s="19"/>
       <c r="E93" s="19" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>583</v>
+        <v>777</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>928</v>
-      </c>
-      <c r="D95" s="19" t="s">
-        <v>929</v>
-      </c>
+        <v>932</v>
+      </c>
+      <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>583</v>
+        <v>777</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>930</v>
-      </c>
-      <c r="D96" s="19"/>
+        <v>933</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>934</v>
+      </c>
       <c r="E96" s="19" t="s">
-        <v>902</v>
+        <v>935</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>931</v>
+        <v>909</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="D97" s="19"/>
+        <v>936</v>
+      </c>
+      <c r="D97" s="19" t="s">
+        <v>937</v>
+      </c>
       <c r="E97" s="19" t="s">
-        <v>933</v>
+        <v>584</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>931</v>
+        <v>909</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>902</v>
+        <v>584</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>931</v>
+        <v>909</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D99" s="19"/>
       <c r="E99" s="19" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>937</v>
-      </c>
-      <c r="D100" s="19" t="s">
-        <v>938</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="D100" s="19"/>
       <c r="E100" s="19" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>939</v>
+        <v>912</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>942</v>
-      </c>
-      <c r="D102" s="19" t="s">
-        <v>943</v>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="D102" s="19"/>
       <c r="E102" s="19" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>945</v>
-      </c>
-      <c r="D103" s="19"/>
+        <v>947</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>948</v>
+      </c>
       <c r="E103" s="19" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>950</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>951</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="D106" s="19"/>
       <c r="E106" s="19" t="s">
-        <v>856</v>
+        <v>943</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>902</v>
+        <v>839</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>649</v>
+        <v>866</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>958</v>
+        <v>908</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>962</v>
+        <v>650</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>958</v>
+        <v>908</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>965</v>
+        <v>912</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>958</v>
+        <v>908</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="C112" s="19" t="s">
         <v>966</v>
@@ -9985,433 +10020,484 @@
         <v>967</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>856</v>
+        <v>650</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>933</v>
+        <v>972</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>933</v>
+        <v>975</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>962</v>
+        <v>866</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>864</v>
+        <v>943</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>979</v>
-      </c>
-      <c r="D118" s="19"/>
+        <v>982</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>983</v>
+      </c>
       <c r="E118" s="19" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>983</v>
-      </c>
-      <c r="D120" s="19"/>
+        <v>986</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>987</v>
+      </c>
       <c r="E120" s="19" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>984</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>985</v>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="D121" s="19"/>
       <c r="E121" s="19" t="s">
-        <v>649</v>
+        <v>990</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>988</v>
+        <v>650</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D123" s="19"/>
       <c r="E123" s="19" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>991</v>
+        <v>969</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>992</v>
-      </c>
-      <c r="D124" s="19"/>
+        <v>994</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>995</v>
+      </c>
       <c r="E124" s="19" t="s">
-        <v>993</v>
+        <v>650</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
+        <v>968</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>969</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>996</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>997</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="19" t="s">
+        <v>968</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>969</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19" t="s">
         <v>990</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>991</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>994</v>
-      </c>
-      <c r="D125" s="19" t="s">
-        <v>995</v>
-      </c>
-      <c r="E125" s="19" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="19" t="s">
-        <v>990</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>991</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>996</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>997</v>
-      </c>
-      <c r="E126" s="19" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>1000</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="D127" s="19"/>
       <c r="E127" s="19" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>993</v>
+        <v>839</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>838</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>856</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D131" s="19"/>
+        <v>1012</v>
+      </c>
+      <c r="D131" s="19" t="s">
+        <v>1013</v>
+      </c>
       <c r="E131" s="19" t="s">
-        <v>838</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>939</v>
+        <v>866</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="D134" s="19"/>
       <c r="E134" s="19" t="s">
-        <v>993</v>
+        <v>839</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D135" s="19"/>
+        <v>1019</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>1020</v>
+      </c>
       <c r="E135" s="19" t="s">
-        <v>993</v>
+        <v>839</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D136" s="19"/>
+        <v>1021</v>
+      </c>
+      <c r="D136" s="19" t="s">
+        <v>1022</v>
+      </c>
       <c r="E136" s="19" t="s">
-        <v>998</v>
+        <v>949</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="D137" s="19"/>
       <c r="E137" s="19" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="D138" s="19"/>
       <c r="E138" s="19" t="s">
-        <v>993</v>
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D139" s="19"/>
+      <c r="E139" s="19" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D140" s="19"/>
+      <c r="E140" s="19" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D141" s="19"/>
+      <c r="E141" s="19" t="s">
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E138"/>
+  <autoFilter ref="A1:E141"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1028">
   <si>
-    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.5.0</t>
+    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.5.1</t>
   </si>
   <si>
     <t xml:space="preserve">Spécification NCS/00/I/COMMON----/ES/010 Rev. A (13/10/2026) — relecture : Sébastien Kubasik — état au 28/10/2026</t>
@@ -7268,7 +7268,7 @@
         <v>561</v>
       </c>
       <c r="D2" s="19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="19" t="n">
         <v>5</v>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1028">
   <si>
-    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 2.5.1</t>
+    <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 1.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">Spécification NCS/00/I/COMMON----/ES/010 Rev. A (13/10/2026) — relecture : Sébastien Kubasik — état au 28/10/2026</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">Que faire d'une ligne incomplète, d'un en-tête absent ou répété, d'un horodatage aberrant ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Une ligne au mauvais nombre de champs est rejetée et listée (jamais complétée : sa dernière valeur pourrait être tronquée). Sans en-tête, la 1re ligne de mesures est gardée (colonnes Colonne_1…). Un en-tête répété (fichiers concaténés) est ignoré. Un horodatage isolé à plus de 10 périodes de ses deux voisins (qui se suivent normalement) est déclaré aberrant : ERREUR, exclu du seul calcul du raster (au lieu d'un faux retour arrière suivi d'un faux trou). Depuis la 2.3.0, il reste affiché à son instant brut sur les courbes (la vue initiale est cadrée sans lui) ; case « Masquer » par fichier dans Base de temps &gt; Configurer. Valeur de 10 périodes arbitraire, réglable dans Outils &gt; Préférences (aberrant_jump_periods) : à valider. Pour une heure hh:mm:ss, une valeur isolée à plus de 12 h de ses voisins, vers l'arrière ou vers l'avant (2.2.0), n'est jamais comptée comme un passage de minuit.</t>
+    <t xml:space="preserve">Une ligne au mauvais nombre de champs est rejetée et listée (jamais complétée : sa dernière valeur pourrait être tronquée). Sans en-tête, la 1re ligne de mesures est gardée (colonnes Colonne_1…). Un en-tête répété (fichiers concaténés) est ignoré. Un horodatage isolé à plus de 10 périodes de ses deux voisins (qui se suivent normalement) est déclaré aberrant : ERREUR, exclu du seul calcul du raster (au lieu d'un faux retour arrière suivi d'un faux trou). Il reste affiché à son instant brut sur les courbes (la vue initiale est cadrée sans lui) ; case « Masquer » par fichier dans Base de temps &gt; Configurer. Valeur de 10 périodes arbitraire, réglable dans Outils &gt; Préférences (aberrant_jump_periods) : à valider. Pour une heure hh:mm:ss, une valeur isolée à plus de 12 h de ses voisins, vers l'arrière ou vers l'avant, n'est jamais comptée comme un passage de minuit.</t>
   </si>
   <si>
     <t xml:space="preserve">core/csv_reader.py, core/time_base.py (OUTLIER_JUMP), config.py (aberrant_jump_periods), core/time_parser.py (_day_offsets)</t>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -21,11 +21,11 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Points ouverts'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Points ouverts'!$A$1:$F$19</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Programmes!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Programmes!$A$1:$F$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Programmes!$A$1:$F$48</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Requis!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Requis!$A$1:$L$65</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Tests!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$141</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$145</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1046">
   <si>
     <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 1.0.0</t>
   </si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (140 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (144 tests, tous OK).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 140/140 tests OK (Python 3.11 de référence,</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 144/144 tests OK (Python 3.11 de référence,</t>
   </si>
   <si>
     <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
@@ -963,7 +963,8 @@
     <t xml:space="preserve">gui/menu_bar.py, gui/path_bar.py</t>
   </si>
   <si>
-    <t xml:space="preserve">test_gui.test_main_window_layout</t>
+    <t xml:space="preserve">test_gui.test_main_window_layout
+test_gui.test_dialogs_speak_french</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5101</t>
@@ -1000,6 +1001,9 @@
     <t xml:space="preserve">gui/status_bar.py, system/activity_log.py</t>
   </si>
   <si>
+    <t xml:space="preserve">test_gui.test_main_window_layout</t>
+  </si>
+  <si>
     <t xml:space="preserve">REQ_COMMON_KH_5103</t>
   </si>
   <si>
@@ -1028,6 +1032,10 @@
   </si>
   <si>
     <t xml:space="preserve">MAIN.py, gui/graph_area.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_gui.test_main_window_layout
+test_gui.test_narrow_window_keeps_every_tool_visible</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5105</t>
@@ -1099,6 +1107,10 @@
     <t xml:space="preserve">Fichiers avec icône de statut</t>
   </si>
   <si>
+    <t xml:space="preserve">test_gui.test_tree_levels_and_types
+test_gui.test_truncated_rows_have_a_tooltip_text</t>
+  </si>
+  <si>
     <t xml:space="preserve">REQ_COMMON_KH_5202</t>
   </si>
   <si>
@@ -1189,7 +1201,8 @@
   </si>
   <si>
     <t xml:space="preserve">test_package_report.test_cursor_labels_show_time_and_value
-test_analysis_tools.test_nearest_and_hold_without_interpolation</t>
+test_analysis_tools.test_nearest_and_hold_without_interpolation
+test_package_report.test_crowded_report_page_stays_readable</t>
   </si>
   <si>
     <t xml:space="preserve">Implémenté — interprétation à valider (état maintenu des Bool)</t>
@@ -1213,7 +1226,8 @@
     <t xml:space="preserve">gui/analysis_tab.py, gui/reading_panel.py, core/readings.py</t>
   </si>
   <si>
-    <t xml:space="preserve">test_gui.test_tracking_mode</t>
+    <t xml:space="preserve">test_gui.test_tracking_mode
+test_gui.test_truncated_rows_have_a_tooltip_text</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5403</t>
@@ -1390,7 +1404,8 @@
   <si>
     <t xml:space="preserve">test_package_report.test_pdf_automatic_and_step_by_step
 test_package_report.test_report_page_layout_like_project_test_reports
-test_gui.test_legend_can_be_moved_hidden_and_picks_curves</t>
+test_gui.test_legend_can_be_moved_hidden_and_picks_curves
+test_package_report.test_crowded_report_page_stays_readable</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_6002</t>
@@ -1967,6 +1982,12 @@
     <t xml:space="preserve">2201, 5406, 5407, 5408, 5500</t>
   </si>
   <si>
+    <t xml:space="preserve">ptbg/gui/dialogs/base.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base commune des boîtes de dialogue : boutons en français.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ptbg/gui/dialogs/report_dialogs.py</t>
   </si>
   <si>
@@ -2054,6 +2075,12 @@
     <t xml:space="preserve">4105</t>
   </si>
   <si>
+    <t xml:space="preserve">ptbg/gui/tooltip.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulle d'aide des tableaux (arbre des données, panneau de lecture).</t>
+  </si>
+  <si>
     <t xml:space="preserve">ptbg/gui/tree_panel.py</t>
   </si>
   <si>
@@ -2630,6 +2657,30 @@
     <t xml:space="preserve">5406</t>
   </si>
   <si>
+    <t xml:space="preserve">test_dialogs_speak_french</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5100 : les dialogues de l'outil affichent « OK » / « Annuler » (et non</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_narrow_window_keeps_every_tool_visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5104 / 5106 : fenêtre étroite, la barre d'outils de l'onglet passe à la ligne :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5104, 5106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_truncated_rows_have_a_tooltip_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5201 / 5402 : une ligne tronquée de l'arbre ou du panneau de lecture a une</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5201, 5402</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_reset_view_returns_to_full_duration</t>
   </si>
   <si>
@@ -2805,6 +2856,15 @@
   </si>
   <si>
     <t xml:space="preserve">2200, 5104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_crowded_report_page_stays_readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 6001 / 5401 / 4102 : page à 4 axes de pistes logiques, deux doubles curseurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4102, 5401, 6001</t>
   </si>
   <si>
     <t xml:space="preserve">test_report_page_layout_like_project_test_reports</t>
@@ -3987,8 +4047,8 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="n">
-        <f aca="false">COUNTA(Tests!$C$2:$C$141)</f>
-        <v>140</v>
+        <f aca="false">COUNTA(Tests!$C$2:$C$145)</f>
+        <v>144</v>
       </c>
       <c r="C15" s="13"/>
     </row>
@@ -3997,8 +4057,8 @@
         <v>16</v>
       </c>
       <c r="B16" s="12" t="n">
-        <f aca="false">COUNTA(Programmes!$A$2:$A$46)</f>
-        <v>45</v>
+        <f aca="false">COUNTA(Programmes!$A$2:$A$48)</f>
+        <v>47</v>
       </c>
       <c r="C16" s="13"/>
     </row>
@@ -5721,7 +5781,7 @@
         <v>292</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>5</v>
@@ -5786,7 +5846,7 @@
         <v>303</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="I40" s="19" t="n">
         <v>1</v>
@@ -5804,23 +5864,23 @@
         <v>24</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="I41" s="19" t="n">
         <v>1</v>
@@ -5838,26 +5898,26 @@
         <v>24</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="I42" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="19" t="s">
         <v>5</v>
@@ -5872,23 +5932,23 @@
         <v>24</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I43" s="19" t="n">
         <v>1</v>
@@ -5906,23 +5966,23 @@
         <v>24</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I44" s="19" t="n">
         <v>4</v>
@@ -5940,23 +6000,23 @@
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I45" s="19" t="n">
         <v>1</v>
@@ -5974,26 +6034,26 @@
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="I46" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="19" t="s">
         <v>5</v>
@@ -6008,23 +6068,23 @@
         <v>25</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>2</v>
@@ -6033,10 +6093,10 @@
         <v>6</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6044,23 +6104,23 @@
         <v>25</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I48" s="19" t="n">
         <v>1</v>
@@ -6078,23 +6138,23 @@
         <v>26</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>2</v>
@@ -6112,23 +6172,23 @@
         <v>27</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I50" s="19" t="n">
         <v>1</v>
@@ -6141,40 +6201,40 @@
       </c>
       <c r="L50" s="19"/>
     </row>
-    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" s="19" t="s">
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6182,26 +6242,26 @@
         <v>27</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="19" t="s">
         <v>5</v>
@@ -6216,23 +6276,23 @@
         <v>27</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I53" s="19" t="n">
         <v>2</v>
@@ -6250,23 +6310,23 @@
         <v>27</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F54" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="H54" s="19" t="s">
         <v>382</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>379</v>
       </c>
       <c r="I54" s="19" t="n">
         <v>2</v>
@@ -6275,10 +6335,10 @@
         <v>6</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6286,23 +6346,23 @@
         <v>27</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I55" s="19" t="n">
         <v>1</v>
@@ -6320,23 +6380,23 @@
         <v>27</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I56" s="19" t="n">
         <v>2</v>
@@ -6354,23 +6414,23 @@
         <v>27</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="19" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I57" s="19" t="n">
         <v>2</v>
@@ -6379,10 +6439,10 @@
         <v>6</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6390,23 +6450,23 @@
         <v>27</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>2</v>
@@ -6415,10 +6475,10 @@
         <v>6</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6426,23 +6486,23 @@
         <v>28</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>1</v>
@@ -6451,10 +6511,10 @@
         <v>7</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6462,23 +6522,23 @@
         <v>29</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I60" s="19" t="n">
         <v>1</v>
@@ -6491,31 +6551,31 @@
       </c>
       <c r="L60" s="19"/>
     </row>
-    <row r="61" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" s="19" t="s">
         <v>5</v>
@@ -6530,23 +6590,23 @@
         <v>29</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>1</v>
@@ -6564,23 +6624,23 @@
         <v>29</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="H63" s="19" t="s">
         <v>439</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>436</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>1</v>
@@ -6598,23 +6658,23 @@
         <v>29</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>1</v>
@@ -6632,23 +6692,23 @@
         <v>29</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>2</v>
@@ -6657,10 +6717,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6712,25 +6772,25 @@
         <v>40</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6738,19 +6798,19 @@
         <v>137</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
@@ -6764,22 +6824,22 @@
         <v>179</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>187</v>
@@ -6790,19 +6850,19 @@
         <v>188</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
@@ -6816,25 +6876,25 @@
         <v>209</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -6867,22 +6927,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,16 +6950,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6908,16 +6968,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6926,13 +6986,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>193</v>
@@ -6944,13 +7004,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>220</v>
@@ -6962,16 +7022,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -6980,16 +7040,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -6998,16 +7058,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -7016,16 +7076,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -7034,16 +7094,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -7052,16 +7112,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7070,16 +7130,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -7088,16 +7148,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7106,16 +7166,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7124,13 +7184,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>122</v>
@@ -7142,16 +7202,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7160,16 +7220,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7178,16 +7238,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7196,16 +7256,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7227,7 +7287,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -7239,33 +7299,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>80</v>
@@ -7274,18 +7334,18 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>130</v>
@@ -7294,18 +7354,18 @@
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>567</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>564</v>
-      </c>
       <c r="C4" s="19" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7314,18 +7374,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7334,18 +7394,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7354,18 +7414,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7374,18 +7434,18 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>138</v>
@@ -7394,18 +7454,18 @@
         <v>7</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7414,18 +7474,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7434,18 +7494,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7454,18 +7514,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7474,18 +7534,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7494,18 +7554,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7514,18 +7574,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7534,18 +7594,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7554,18 +7614,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7574,18 +7634,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7594,322 +7654,318 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>616</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>613</v>
-      </c>
       <c r="C20" s="19" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>69</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E21" s="19" t="n">
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>624</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="19"/>
+        <v>14</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D26" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="D27" s="19" t="n">
         <v>227</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E27" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F26" s="19" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>636</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="D27" s="19" t="n">
+      <c r="F27" s="19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="D28" s="19" t="n">
         <v>93</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="19" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>639</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>640</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>35</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>3</v>
-      </c>
       <c r="F28" s="19" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D32" s="19" t="n">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>655</v>
+        <v>616</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D33" s="19" t="n">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>657</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
         <v>658</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>655</v>
+        <v>616</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>659</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>480</v>
+        <v>204</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F34" s="19" t="s">
         <v>660</v>
@@ -7920,92 +7976,92 @@
         <v>661</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="19"/>
+        <v>10</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>31</v>
+        <v>564</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="19"/>
+        <v>34</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D37" s="19" t="n">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>668</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>671</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>672</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="B39" s="19" t="s">
         <v>673</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>670</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>674</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39" s="19" t="s">
         <v>675</v>
@@ -8016,143 +8072,183 @@
         <v>676</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D40" s="19" t="n">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>560</v>
+        <v>677</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D41" s="19" t="n">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>201</v>
+        <v>683</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>201</v>
+        <v>677</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D42" s="19" t="n">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>685</v>
+        <v>563</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D43" s="19" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E43" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>687</v>
+        <v>201</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>685</v>
+        <v>201</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D44" s="19" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E44" s="19" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B45" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>685</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>691</v>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>101</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D46" s="19" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E46" s="19" t="n">
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>695</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="19" t="s">
+        <v>697</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>698</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>101</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F48"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8169,7 +8265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -8181,2323 +8277,2391 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="D8" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>714</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>845</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>868</v>
+        <v>826</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>868</v>
+        <v>826</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>868</v>
+        <v>826</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>875</v>
-      </c>
-      <c r="D69" s="19"/>
+        <v>879</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>880</v>
+      </c>
       <c r="E69" s="19" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>879</v>
-      </c>
-      <c r="D71" s="19"/>
+        <v>887</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>888</v>
+      </c>
       <c r="E71" s="19" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>881</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>882</v>
-      </c>
+        <v>890</v>
+      </c>
+      <c r="D72" s="19"/>
       <c r="E72" s="19" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>888</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>889</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="D74" s="19"/>
       <c r="E74" s="19" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>836</v>
+        <v>898</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>901</v>
+        <v>843</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>913</v>
-      </c>
-      <c r="D82" s="19"/>
+        <v>917</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>918</v>
+      </c>
       <c r="E82" s="19" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>912</v>
+        <v>922</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>781</v>
+        <v>925</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>787</v>
+        <v>930</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="D86" s="19"/>
       <c r="E86" s="19" t="s">
-        <v>787</v>
+        <v>930</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>921</v>
-      </c>
-      <c r="D87" s="19"/>
+        <v>932</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>933</v>
+      </c>
       <c r="E87" s="19" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>922</v>
-      </c>
-      <c r="D88" s="19"/>
+        <v>934</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>935</v>
+      </c>
       <c r="E88" s="19" t="s">
-        <v>912</v>
+        <v>788</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>912</v>
+        <v>794</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="19" t="s">
-        <v>584</v>
+        <v>794</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>926</v>
-      </c>
-      <c r="D91" s="19" t="s">
-        <v>927</v>
-      </c>
+        <v>939</v>
+      </c>
+      <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>929</v>
-      </c>
-      <c r="D93" s="19"/>
+        <v>941</v>
+      </c>
+      <c r="D93" s="19" t="s">
+        <v>942</v>
+      </c>
       <c r="E93" s="19" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>930</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>931</v>
-      </c>
+        <v>943</v>
+      </c>
+      <c r="D94" s="19"/>
       <c r="E94" s="19" t="s">
-        <v>777</v>
+        <v>587</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="D95" s="19"/>
+        <v>944</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>945</v>
+      </c>
       <c r="E95" s="19" t="s">
-        <v>777</v>
+        <v>930</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>933</v>
-      </c>
-      <c r="D96" s="19" t="s">
-        <v>934</v>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="D96" s="19"/>
       <c r="E96" s="19" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>936</v>
-      </c>
-      <c r="D97" s="19" t="s">
-        <v>937</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>584</v>
+        <v>930</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>584</v>
+        <v>784</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="D99" s="19"/>
       <c r="E99" s="19" t="s">
-        <v>912</v>
+        <v>784</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>942</v>
-      </c>
-      <c r="D100" s="19"/>
+        <v>951</v>
+      </c>
+      <c r="D100" s="19" t="s">
+        <v>952</v>
+      </c>
       <c r="E100" s="19" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>912</v>
+        <v>587</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>946</v>
-      </c>
-      <c r="D102" s="19"/>
+        <v>956</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>957</v>
+      </c>
       <c r="E102" s="19" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>947</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>948</v>
-      </c>
+        <v>958</v>
+      </c>
+      <c r="D103" s="19"/>
       <c r="E103" s="19" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>950</v>
-      </c>
-      <c r="D104" s="19" t="s">
-        <v>951</v>
-      </c>
+        <v>960</v>
+      </c>
+      <c r="D104" s="19"/>
       <c r="E104" s="19" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="D106" s="19"/>
       <c r="E106" s="19" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>912</v>
+        <v>967</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>839</v>
+        <v>967</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="D109" s="19" t="s">
+        <v>971</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="19" t="s">
+        <v>926</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>959</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>973</v>
+      </c>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19" t="s">
         <v>961</v>
-      </c>
-      <c r="E109" s="19" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="19" t="s">
-        <v>908</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>941</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>962</v>
-      </c>
-      <c r="D110" s="19" t="s">
-        <v>963</v>
-      </c>
-      <c r="E110" s="19" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>650</v>
+        <v>846</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>968</v>
+        <v>926</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>972</v>
+        <v>881</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>968</v>
+        <v>926</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>975</v>
+        <v>655</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>968</v>
+        <v>926</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>866</v>
+        <v>930</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>968</v>
+        <v>926</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>943</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C120" s="19" t="s">
+        <v>996</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>997</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="19" t="s">
         <v>986</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="B121" s="19" t="s">
         <v>987</v>
       </c>
-      <c r="E120" s="19" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>969</v>
-      </c>
       <c r="C121" s="19" t="s">
-        <v>989</v>
-      </c>
-      <c r="D121" s="19"/>
+        <v>998</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>999</v>
+      </c>
       <c r="E121" s="19" t="s">
-        <v>990</v>
+        <v>961</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>993</v>
-      </c>
-      <c r="D123" s="19"/>
+        <v>1002</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>1003</v>
+      </c>
       <c r="E123" s="19" t="s">
-        <v>990</v>
+        <v>889</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>996</v>
-      </c>
-      <c r="D125" s="19" t="s">
-        <v>997</v>
-      </c>
+        <v>1007</v>
+      </c>
+      <c r="D125" s="19"/>
       <c r="E125" s="19" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="D126" s="19"/>
+        <v>1009</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>1010</v>
+      </c>
       <c r="E126" s="19" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="D127" s="19"/>
       <c r="E127" s="19" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>839</v>
+        <v>655</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="E129" s="19" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>987</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D130" s="19"/>
+      <c r="E130" s="19" t="s">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="19" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B130" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C130" s="19" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D130" s="19" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E130" s="19" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D131" s="19" t="s">
-        <v>1013</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="D131" s="19"/>
       <c r="E131" s="19" t="s">
-        <v>1003</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>866</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D134" s="19"/>
+        <v>1027</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>1028</v>
+      </c>
       <c r="E134" s="19" t="s">
-        <v>839</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>839</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>949</v>
+        <v>846</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D137" s="19"/>
+        <v>1034</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>1035</v>
+      </c>
       <c r="E137" s="19" t="s">
-        <v>1003</v>
+        <v>881</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="D138" s="19"/>
       <c r="E138" s="19" t="s">
-        <v>1003</v>
+        <v>846</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D139" s="19"/>
+        <v>1037</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>1038</v>
+      </c>
       <c r="E139" s="19" t="s">
-        <v>1008</v>
+        <v>846</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D140" s="19"/>
+        <v>1039</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>1040</v>
+      </c>
       <c r="E140" s="19" t="s">
-        <v>1003</v>
+        <v>967</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="19" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="D141" s="19"/>
       <c r="E141" s="19" t="s">
-        <v>1003</v>
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D142" s="19"/>
+      <c r="E142" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D143" s="19"/>
+      <c r="E143" s="19" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D144" s="19"/>
+      <c r="E144" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D145" s="19"/>
+      <c r="E145" s="19" t="s">
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E141"/>
+  <autoFilter ref="A1:E145"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -25,7 +25,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Requis!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Requis!$A$1:$L$65</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Tests!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$145</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tests!$A$1:$E$146</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1049">
   <si>
     <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 1.0.0</t>
   </si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (144 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (145 tests, tous OK).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 144/144 tests OK (Python 3.11 de référence,</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 145/145 tests OK (Python 3.11 de référence,</t>
   </si>
   <si>
     <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
@@ -828,7 +828,8 @@
     <t xml:space="preserve">plotting/monitor.py, plotting/renderer.py</t>
   </si>
   <si>
-    <t xml:space="preserve">test_package_report.test_every_template_has_time_base_monitor</t>
+    <t xml:space="preserve">test_package_report.test_every_template_has_time_base_monitor
+test_gui.test_labels_and_monitor_legend_can_be_moved</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_4103</t>
@@ -1074,7 +1075,8 @@
     <t xml:space="preserve">test_gui.test_xy_tab_and_point_pick
 test_gui.test_tabs_close_with_their_cross
 test_gui.test_reset_view_returns_to_full_duration
-test_gui.test_legend_can_be_moved_hidden_and_picks_curves</t>
+test_gui.test_legend_can_be_moved_hidden_and_picks_curves
+test_gui.test_labels_and_monitor_legend_can_be_moved</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_5200</t>
@@ -1202,7 +1204,8 @@
   <si>
     <t xml:space="preserve">test_package_report.test_cursor_labels_show_time_and_value
 test_analysis_tools.test_nearest_and_hold_without_interpolation
-test_package_report.test_crowded_report_page_stays_readable</t>
+test_package_report.test_crowded_report_page_stays_readable
+test_gui.test_labels_and_monitor_legend_can_be_moved</t>
   </si>
   <si>
     <t xml:space="preserve">Implémenté — interprétation à valider (état maintenu des Bool)</t>
@@ -1405,7 +1408,8 @@
     <t xml:space="preserve">test_package_report.test_pdf_automatic_and_step_by_step
 test_package_report.test_report_page_layout_like_project_test_reports
 test_gui.test_legend_can_be_moved_hidden_and_picks_curves
-test_package_report.test_crowded_report_page_stays_readable</t>
+test_package_report.test_crowded_report_page_stays_readable
+test_gui.test_labels_and_monitor_legend_can_be_moved</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_6002</t>
@@ -2655,6 +2659,15 @@
   </si>
   <si>
     <t xml:space="preserve">5406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_labels_and_monitor_legend_can_be_moved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ 5106 / 5401 / 4102 / 6001 : noms des pistes logiques, étiquettes des curseurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4102, 5106, 5401, 6001</t>
   </si>
   <si>
     <t xml:space="preserve">test_dialogs_speak_french</t>
@@ -4047,8 +4060,8 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="n">
-        <f aca="false">COUNTA(Tests!$C$2:$C$145)</f>
-        <v>144</v>
+        <f aca="false">COUNTA(Tests!$C$2:$C$146)</f>
+        <v>145</v>
       </c>
       <c r="C15" s="13"/>
     </row>
@@ -5573,7 +5586,7 @@
         <v>252</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="19" t="s">
         <v>5</v>
@@ -5961,7 +5974,7 @@
       </c>
       <c r="L43" s="19"/>
     </row>
-    <row r="44" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -5985,7 +5998,7 @@
         <v>327</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44" s="19" t="s">
         <v>5</v>
@@ -6201,7 +6214,7 @@
       </c>
       <c r="L50" s="19"/>
     </row>
-    <row r="51" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
         <v>27</v>
       </c>
@@ -6225,7 +6238,7 @@
         <v>368</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="19" t="s">
         <v>6</v>
@@ -6551,7 +6564,7 @@
       </c>
       <c r="L60" s="19"/>
     </row>
-    <row r="61" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
         <v>29</v>
       </c>
@@ -6575,7 +6588,7 @@
         <v>433</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" s="19" t="s">
         <v>5</v>
@@ -7348,7 +7361,7 @@
         <v>568</v>
       </c>
       <c r="D3" s="19" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3" s="19" t="n">
         <v>13</v>
@@ -7668,10 +7681,10 @@
         <v>617</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>618</v>
@@ -7688,7 +7701,7 @@
         <v>620</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E20" s="19" t="n">
         <v>69</v>
@@ -7982,7 +7995,7 @@
         <v>663</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E35" s="19" t="n">
         <v>10</v>
@@ -8002,10 +8015,10 @@
         <v>666</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F36" s="19" t="s">
         <v>667</v>
@@ -8265,7 +8278,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -9243,7 +9256,7 @@
         <v>851</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>646</v>
+        <v>852</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9254,13 +9267,13 @@
         <v>826</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>854</v>
+        <v>646</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9418,27 +9431,27 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
+        <v>821</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="C70" s="19" t="s">
         <v>882</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="D70" s="19" t="s">
         <v>883</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="E70" s="19" t="s">
         <v>884</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>885</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>887</v>
@@ -9452,74 +9465,74 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>890</v>
       </c>
-      <c r="D72" s="19"/>
+      <c r="D72" s="19" t="s">
+        <v>891</v>
+      </c>
       <c r="E72" s="19" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>891</v>
-      </c>
-      <c r="D73" s="19" t="s">
+        <v>893</v>
+      </c>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19" t="s">
         <v>892</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>894</v>
       </c>
-      <c r="D74" s="19"/>
+      <c r="D74" s="19" t="s">
+        <v>895</v>
+      </c>
       <c r="E74" s="19" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>896</v>
-      </c>
-      <c r="D75" s="19" t="s">
         <v>897</v>
       </c>
+      <c r="D75" s="19"/>
       <c r="E75" s="19" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C76" s="19" t="s">
         <v>899</v>
@@ -9533,27 +9546,27 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B77" s="19" t="s">
+        <v>886</v>
+      </c>
+      <c r="C77" s="19" t="s">
         <v>902</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="D77" s="19" t="s">
         <v>903</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="E77" s="19" t="s">
         <v>904</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>906</v>
@@ -9562,32 +9575,32 @@
         <v>907</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>843</v>
+        <v>908</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>910</v>
+        <v>843</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C80" s="19" t="s">
         <v>911</v>
@@ -9601,10 +9614,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C81" s="19" t="s">
         <v>914</v>
@@ -9618,10 +9631,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>917</v>
@@ -9635,10 +9648,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C83" s="19" t="s">
         <v>920</v>
@@ -9652,10 +9665,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>923</v>
@@ -9669,266 +9682,266 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
+        <v>885</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>905</v>
+      </c>
+      <c r="C85" s="19" t="s">
         <v>926</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="D85" s="19" t="s">
         <v>927</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="E85" s="19" t="s">
         <v>928</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>929</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C86" s="19" t="s">
         <v>931</v>
       </c>
-      <c r="D86" s="19"/>
+      <c r="D86" s="19" t="s">
+        <v>932</v>
+      </c>
       <c r="E86" s="19" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="D87" s="19" t="s">
+        <v>934</v>
+      </c>
+      <c r="D87" s="19"/>
+      <c r="E87" s="19" t="s">
         <v>933</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>788</v>
+        <v>933</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>938</v>
-      </c>
-      <c r="D90" s="19"/>
+        <v>939</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>940</v>
+      </c>
       <c r="E90" s="19" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>930</v>
+        <v>794</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>941</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>942</v>
-      </c>
+        <v>943</v>
+      </c>
+      <c r="D93" s="19"/>
       <c r="E93" s="19" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>943</v>
-      </c>
-      <c r="D94" s="19"/>
+        <v>944</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>945</v>
+      </c>
       <c r="E94" s="19" t="s">
-        <v>587</v>
+        <v>933</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>944</v>
-      </c>
-      <c r="D95" s="19" t="s">
-        <v>945</v>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>930</v>
+        <v>587</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>946</v>
-      </c>
-      <c r="D96" s="19"/>
+        <v>947</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>948</v>
+      </c>
       <c r="E96" s="19" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>948</v>
-      </c>
-      <c r="D98" s="19" t="s">
-        <v>949</v>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>784</v>
+        <v>933</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>950</v>
-      </c>
-      <c r="D99" s="19"/>
+        <v>951</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>952</v>
+      </c>
       <c r="E99" s="19" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>951</v>
-      </c>
-      <c r="D100" s="19" t="s">
-        <v>952</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="D100" s="19"/>
       <c r="E100" s="19" t="s">
-        <v>953</v>
+        <v>784</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C101" s="19" t="s">
         <v>954</v>
@@ -9937,21 +9950,21 @@
         <v>955</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>587</v>
+        <v>956</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>587</v>
@@ -9959,89 +9972,89 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>958</v>
-      </c>
-      <c r="D103" s="19"/>
+        <v>959</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>960</v>
+      </c>
       <c r="E103" s="19" t="s">
-        <v>930</v>
+        <v>587</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>959</v>
+        <v>930</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D104" s="19"/>
       <c r="E104" s="19" t="s">
-        <v>961</v>
+        <v>933</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>962</v>
-      </c>
-      <c r="D105" s="19" t="s">
         <v>963</v>
       </c>
+      <c r="D105" s="19"/>
       <c r="E105" s="19" t="s">
-        <v>930</v>
+        <v>964</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>964</v>
-      </c>
-      <c r="D106" s="19"/>
+        <v>965</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>966</v>
+      </c>
       <c r="E106" s="19" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>965</v>
-      </c>
-      <c r="D107" s="19" t="s">
-        <v>966</v>
-      </c>
+        <v>967</v>
+      </c>
+      <c r="D107" s="19"/>
       <c r="E107" s="19" t="s">
-        <v>967</v>
+        <v>933</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C108" s="19" t="s">
         <v>968</v>
@@ -10050,166 +10063,166 @@
         <v>969</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C109" s="19" t="s">
+        <v>971</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="E109" s="19" t="s">
         <v>970</v>
       </c>
-      <c r="D109" s="19" t="s">
-        <v>971</v>
-      </c>
-      <c r="E109" s="19" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C110" s="19" t="s">
         <v>973</v>
       </c>
-      <c r="D110" s="19"/>
+      <c r="D110" s="19" t="s">
+        <v>974</v>
+      </c>
       <c r="E110" s="19" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>974</v>
-      </c>
-      <c r="D111" s="19" t="s">
-        <v>975</v>
-      </c>
+        <v>976</v>
+      </c>
+      <c r="D111" s="19"/>
       <c r="E111" s="19" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E112" s="19" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="19" t="s">
+        <v>929</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>962</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>980</v>
+      </c>
+      <c r="E113" s="19" t="s">
         <v>846</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="19" t="s">
-        <v>926</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>959</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>978</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>979</v>
-      </c>
-      <c r="E113" s="19" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>655</v>
+        <v>884</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>930</v>
+        <v>655</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>655</v>
+        <v>933</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>986</v>
+        <v>929</v>
       </c>
       <c r="B117" s="19" t="s">
+        <v>962</v>
+      </c>
+      <c r="C117" s="19" t="s">
         <v>987</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="D117" s="19" t="s">
         <v>988</v>
       </c>
-      <c r="D117" s="19" t="s">
-        <v>989</v>
-      </c>
       <c r="E117" s="19" t="s">
-        <v>990</v>
+        <v>655</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C118" s="19" t="s">
         <v>991</v>
@@ -10223,10 +10236,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C119" s="19" t="s">
         <v>994</v>
@@ -10235,245 +10248,245 @@
         <v>995</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>881</v>
+        <v>996</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>961</v>
+        <v>884</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>990</v>
+        <v>964</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>889</v>
+        <v>993</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C125" s="19" t="s">
         <v>1007</v>
       </c>
-      <c r="D125" s="19"/>
+      <c r="D125" s="19" t="s">
+        <v>1008</v>
+      </c>
       <c r="E125" s="19" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D126" s="19" t="s">
         <v>1010</v>
       </c>
+      <c r="D126" s="19"/>
       <c r="E126" s="19" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="19" t="s">
+        <v>989</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E127" s="19" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="19" t="s">
-        <v>986</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>987</v>
-      </c>
-      <c r="C127" s="19" t="s">
+    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="19" t="s">
+        <v>989</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D128" s="19"/>
+      <c r="E128" s="19" t="s">
         <v>1011</v>
-      </c>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="19" t="s">
-        <v>986</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>987</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E128" s="19" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C130" s="19" t="s">
         <v>1017</v>
       </c>
-      <c r="D130" s="19"/>
+      <c r="D130" s="19" t="s">
+        <v>1018</v>
+      </c>
       <c r="E130" s="19" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>1018</v>
+        <v>989</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>1019</v>
+        <v>990</v>
       </c>
       <c r="C131" s="19" t="s">
         <v>1020</v>
       </c>
       <c r="D131" s="19"/>
       <c r="E131" s="19" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D132" s="19" t="s">
         <v>1023</v>
       </c>
+      <c r="D132" s="19"/>
       <c r="E132" s="19" t="s">
-        <v>846</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>1026</v>
+        <v>846</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C134" s="19" t="s">
         <v>1027</v>
@@ -10487,10 +10500,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C135" s="19" t="s">
         <v>1030</v>
@@ -10499,169 +10512,186 @@
         <v>1031</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>846</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>881</v>
+        <v>846</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D138" s="19"/>
+        <v>1037</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>1038</v>
+      </c>
       <c r="E138" s="19" t="s">
-        <v>846</v>
+        <v>884</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D139" s="19" t="s">
-        <v>1038</v>
-      </c>
+        <v>1039</v>
+      </c>
+      <c r="D139" s="19"/>
       <c r="E139" s="19" t="s">
         <v>846</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>967</v>
+        <v>846</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D141" s="19"/>
+        <v>1042</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>1043</v>
+      </c>
       <c r="E141" s="19" t="s">
-        <v>1021</v>
+        <v>970</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D142" s="19"/>
       <c r="E142" s="19" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D143" s="19"/>
       <c r="E143" s="19" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D144" s="19"/>
       <c r="E144" s="19" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="19" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B145" s="19" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D145" s="19"/>
       <c r="E145" s="19" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="19" t="s">
         <v>1021</v>
       </c>
+      <c r="B146" s="19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D146" s="19"/>
+      <c r="E146" s="19" t="s">
+        <v>1024</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E145"/>
+  <autoFilter ref="A1:E146"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -704,7 +704,7 @@
     <t xml:space="preserve">Paquets documentés et alignés sur la version du noyau Python</t>
   </si>
   <si>
-    <t xml:space="preserve">requirements.txt figé et commenté, docs/DEPENDANCES.md (versions, licences, Python supportés, wheels, impacts de montée de version), relevé au démarrage</t>
+    <t xml:space="preserve">requirements.txt figé et commenté, docs/DEPENDANCES.md (versions, licences, Python supportés, wheels, impacts de montée de version) et classeur docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (dépendances, sensibilités Python / OS / 32-64 bits, campagnes, relevé des postes), relevé au démarrage</t>
   </si>
   <si>
     <t xml:space="preserve">system/environment.py, requirements.txt</t>
@@ -1548,10 +1548,10 @@
     <t xml:space="preserve">Il y a des packages transverses toute version et d’autre plus restrictifs avec independances. Le plus fréquemment il y a une sensibilité à la version de python, l’OS, et le cœur 32 ou 63 bits</t>
   </si>
   <si>
-    <t xml:space="preserve">Sensibilités relevées par Sébastien traitées : versions figées dans requirements.txt (identiques Python 3.11 à 3.14, Windows et SLES) ; DEPENDANCES.md donne pour chaque paquet la version, le type (direct / transitif), les Python supportés, les wheels win_amd64 / manylinux, la licence, et distingue les composants compilés (sensibles à Python, à l'OS et au 32/64 bits : numpy, matplotlib, contourpy, kiwisolver, pillow) du Python pur. Cible 64 bits uniquement. Relevé des versions au démarrage et outil d'audit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requirements.txt ; docs/DEPENDANCES.md ; ptbg/system/environment.py ; tools/audit_environnement.py</t>
+    <t xml:space="preserve">Sensibilités relevées par Sébastien traitées : versions figées dans requirements.txt (identiques Python 3.11 à 3.14, Windows et SLES) ; DEPENDANCES.md donne pour chaque paquet la version, le type (direct / transitif), les Python supportés, les wheels win_amd64 / manylinux, la licence, et distingue les composants compilés (sensibles à Python, à l'OS et au 32/64 bits : numpy, matplotlib, contourpy, fonttools, kiwisolver, pillow) du Python pur. Cible 64 bits uniquement. Relevé des versions au démarrage et outil d'audit. Classeur dédié docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (bibliothèques, dépendances, sensibilités, campagnes de tests, impact d'une montée de version, relevé des postes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requirements.txt ; docs/DEPENDANCES.md ; docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx ; ptbg/system/environment.py ; tools/audit_environnement.py</t>
   </si>
   <si>
     <t xml:space="preserve">test_architecture.test_third_party_libraries_are_documented_and_pinned</t>
@@ -6884,7 +6884,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
         <v>209</v>
       </c>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1047">
   <si>
     <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 1.0.0</t>
   </si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Lecture des statuts :</t>
   </si>
   <si>
-    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (145 tests, tous OK).</t>
+    <t xml:space="preserve">• Implémenté et testé : fonction présente et associée à au moins un test automatique qui en vérifie un cas représentatif (145 tests fournis).</t>
   </si>
   <si>
     <t xml:space="preserve">  Un test associé ne prouve pas à lui seul que toute l'exigence est satisfaite : la revue des énoncés avec Sébastien le confirmera.</t>
@@ -144,16 +144,16 @@
     <t xml:space="preserve">• Proposition (énoncé vide) : REQ 5500 n'a pas d'énoncé dans la Rev. A ; une fonction est proposée.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Qualification à faire : réalisé et testé sous Linux ; essai à consigner sur Windows 11 / SLES 15 SP7 réels (3000) ou sur volumes réels (4105).</t>
+    <t xml:space="preserve">• Qualification à faire : réalisé et couvert par les tests ; essai à faire sur le poste Windows 11 et la VM Linux SLES 15 SP7 fournie par l'entreprise (3000) ou sur volumes réels (4105).</t>
   </si>
   <si>
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe ; 145/145 tests OK (Python 3.11 de référence,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">et campagne Python 3.10 à 3.14, Tk 8.6 et 9). Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe. Les 145 tests sont à lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sur le poste Windows et sur la VM Linux. Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
   </si>
   <si>
     <t xml:space="preserve">Section du Word</t>
@@ -613,14 +613,13 @@
     <t xml:space="preserve">Compatible SLES 15 SP7 au moins (+ Windows, remarque du relecteur)</t>
   </si>
   <si>
-    <t xml:space="preserve">Python + Tk + numpy + matplotlib, wheels vérifiées pour win_amd64 et manylinux (glibc 2.38 de SP7) ; scripts SLES et Windows ; Spyder 6</t>
+    <t xml:space="preserve">Python + Tk + numpy + matplotlib, wheels disponibles pour win_amd64 et manylinux (glibc 2.38 de SP7) ; scripts SLES et Windows ; Spyder 6</t>
   </si>
   <si>
     <t xml:space="preserve">system/compat.py, install/</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_minimal_python_syntax
-campagne multi-versions</t>
+    <t xml:space="preserve">test_architecture.test_minimal_python_syntax</t>
   </si>
   <si>
     <t xml:space="preserve">Implémenté — qualification sur cible à faire (Windows 11, SLES 15 SP7)</t>
@@ -641,15 +640,12 @@
     <t xml:space="preserve">Compatible Python 3.6 au moins</t>
   </si>
   <si>
-    <t xml:space="preserve">Lu comme « 3.6 minimum » : code vérifié de 3.10 à 3.14, référence 3.11 (décision du relecteur : Python 3.11 sur SLES 15)</t>
+    <t xml:space="preserve">Lu comme « 3.6 minimum » : code prévu pour 3.10 à 3.14, référence 3.11 (décision du relecteur : Python 3.11 sur SLES 15)</t>
   </si>
   <si>
     <t xml:space="preserve">version.py (MIN_PYTHON)</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_minimal_python_syntax</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implémenté — interprétation à valider (3.6 strict exclu)</t>
   </si>
   <si>
@@ -704,7 +700,7 @@
     <t xml:space="preserve">Paquets documentés et alignés sur la version du noyau Python</t>
   </si>
   <si>
-    <t xml:space="preserve">requirements.txt figé et commenté, docs/DEPENDANCES.md (versions, licences, Python supportés, wheels, impacts de montée de version) et classeur docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (dépendances, sensibilités Python / OS / 32-64 bits, campagnes, relevé des postes), relevé au démarrage</t>
+    <t xml:space="preserve">requirements.txt figé et commenté, docs/DEPENDANCES.md (versions, licences, Python supportés, wheels, impacts de montée de version) et classeur docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (ce que l'outil utilise et risque de chaque élément, effets d'une montée de version, tests à réaliser, relevé des postes), relevé au démarrage</t>
   </si>
   <si>
     <t xml:space="preserve">system/environment.py, requirements.txt</t>
@@ -878,7 +874,7 @@
     <t xml:space="preserve">Traitement jamais bloqué ni instable</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture par blocs, annulable, en arrière-plan ; lignes ordinaires découpées d'un coup et colonnes converties en entier (core/vector_parse.py), lignes et cellules particulières traitées une à une avec les mêmes règles (résultats identiques) ; une ligne malade (guillemet non fermé, octets nuls, cellule démesurée) n'atteint jamais la suite ; une erreur imprévue sur un fichier le marque en erreur sans arrêter les autres ; analyse vectorisée O(n) (changements de fréquence et croix des cellules vides compris), événements plafonnés ; curseurs redessinés seuls (blitting), abscisses et nuage X/Y en cache ; axe en défaut remplacé par un message ; banc de 130 fichiers pathologiques et 40 corruptions aléatoires sans exception ; banc de mesure tools/banc_performance.py</t>
+    <t xml:space="preserve">Lecture par blocs, annulable, en arrière-plan ; lignes ordinaires découpées d'un coup et colonnes converties en entier (core/vector_parse.py), lignes et cellules particulières traitées une à une avec les mêmes règles (résultats identiques) ; une ligne malade (guillemet non fermé, octets nuls, cellule démesurée) n'atteint jamais la suite ; une erreur imprévue sur un fichier le marque en erreur sans arrêter les autres ; analyse vectorisée O(n) (changements de fréquence et croix des cellules vides compris), événements plafonnés ; curseurs redessinés seuls (blitting), abscisses et nuage X/Y en cache ; axe en défaut remplacé par un message ; fichiers pathologiques et 40 corruptions aléatoires couverts par les tests ; banc de mesure tools/banc_performance.py</t>
   </si>
   <si>
     <t xml:space="preserve">gui/tasks.py, core/csv_reader.py, core/vector_parse.py, core/data_package.py (load_source), core/time_base.py, core/sampling.py, plotting/renderer.py, gui/analysis_tab.py</t>
@@ -1521,13 +1517,13 @@
     <t xml:space="preserve">Ou Windows!? Besoin de déterminer la cible ou double compatibilité</t>
   </si>
   <si>
-    <t xml:space="preserve">Double compatibilité retenue (décision du demandeur) : Windows 11 64 bits sous Spyder 6 ET SLES 15 SP7. Un seul code ; toutes les différences d'OS isolées dans ptbg/system/compat.py ; scripts d'installation et de lancement pour les deux systèmes ; wheels vérifiées win_amd64 et manylinux (glibc 2.38 de SP7).</t>
+    <t xml:space="preserve">Double compatibilité retenue (décision du demandeur) : Windows 11 64 bits sous Spyder 6 ET SLES 15 SP7. Un seul code ; toutes les différences d'OS isolées dans ptbg/system/compat.py ; scripts d'installation et de lancement pour les deux systèmes ; wheels disponibles win_amd64 et manylinux (glibc 2.38 de SP7).</t>
   </si>
   <si>
     <t xml:space="preserve">ptbg/system/compat.py ; install/ ; docs/COMPATIBILITE_OS.md</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_os_specific_code_is_centralized ; campagne 7 combinaisons (Tk 8.6 et 9)</t>
+    <t xml:space="preserve">test_architecture.test_os_specific_code_is_centralized ; essais à faire sur le poste Windows et la VM Linux SLES fournie par l'entreprise</t>
   </si>
   <si>
     <t xml:space="preserve">Qualification sur cible à faire</t>
@@ -1536,19 +1532,16 @@
     <t xml:space="preserve">Ces versions évolueront forcément, c’est ici le point de départ observé avec le package TDS V1.1.0. Semble possible de disposer d’un upgrade Python3.11 pour SLES 15</t>
   </si>
   <si>
-    <t xml:space="preserve">Python 3.6 lu comme un minimum : référence Python 3.11 (upgrade possible sur SLES 15, comme indiqué), code vérifié de 3.10 à 3.14. Python 3.6 (fin de vie 2021) imposerait numpy 1.19 / matplotlib 3.3 : non retenu. Version minimale contrôlée au lancement par MAIN.py.</t>
+    <t xml:space="preserve">Python 3.6 lu comme un minimum : référence Python 3.11 (upgrade possible sur SLES 15, comme indiqué), code prévu pour 3.10 à 3.14. Python 3.6 (fin de vie 2021) imposerait numpy 1.19 / matplotlib 3.3 : non retenu. Version minimale contrôlée au lancement par MAIN.py.</t>
   </si>
   <si>
     <t xml:space="preserve">ptbg/version.py (MIN_PYTHON) ; MAIN.py</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_minimal_python_syntax ; campagne Python 3.10 → 3.14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Il y a des packages transverses toute version et d’autre plus restrictifs avec independances. Le plus fréquemment il y a une sensibilité à la version de python, l’OS, et le cœur 32 ou 63 bits</t>
   </si>
   <si>
-    <t xml:space="preserve">Sensibilités relevées par Sébastien traitées : versions figées dans requirements.txt (identiques Python 3.11 à 3.14, Windows et SLES) ; DEPENDANCES.md donne pour chaque paquet la version, le type (direct / transitif), les Python supportés, les wheels win_amd64 / manylinux, la licence, et distingue les composants compilés (sensibles à Python, à l'OS et au 32/64 bits : numpy, matplotlib, contourpy, fonttools, kiwisolver, pillow) du Python pur. Cible 64 bits uniquement. Relevé des versions au démarrage et outil d'audit. Classeur dédié docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (bibliothèques, dépendances, sensibilités, campagnes de tests, impact d'une montée de version, relevé des postes).</t>
+    <t xml:space="preserve">Sensibilités relevées par Sébastien traitées : versions figées dans requirements.txt (identiques Python 3.11 à 3.14, Windows et SLES) ; DEPENDANCES.md donne pour chaque paquet la version, le type (direct / transitif), les Python supportés, les wheels win_amd64 / manylinux, la licence, et distingue les composants compilés (sensibles à Python, à l'OS et au 32/64 bits : numpy, matplotlib, contourpy, fonttools, kiwisolver, pillow) du Python pur. Cible 64 bits uniquement. Relevé des versions au démarrage et outil d'audit. Classeur dédié docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx (bibliothèques, dépendances, sensibilités, tests à réaliser, impact d'une montée de version, relevé des postes).</t>
   </si>
   <si>
     <t xml:space="preserve">requirements.txt ; docs/DEPENDANCES.md ; docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx ; ptbg/system/environment.py ; tools/audit_environnement.py</t>
@@ -1608,7 +1601,7 @@
     <t xml:space="preserve">3.6 est-il un minimum ou une cible stricte ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Lu comme un minimum : développement en 3.11, code vérifié de 3.10 à 3.14. Python 3.6 (fin de vie 2021) n'est pas supporté : il imposerait numpy 1.19 / matplotlib 3.3.</t>
+    <t xml:space="preserve">Lu comme un minimum : développement en 3.11, code prévu pour 3.10 à 3.14. Python 3.6 (fin de vie 2021) n'est pas supporté : il imposerait numpy 1.19 / matplotlib 3.3.</t>
   </si>
   <si>
     <t xml:space="preserve">REQ_COMMON_KH_3000 (commentaire « ou Windows ? double compatibilité »)</t>
@@ -5271,7 +5264,7 @@
         <v>193</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>1</v>
@@ -5280,10 +5273,10 @@
         <v>6</v>
       </c>
       <c r="K23" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="L23" s="19" t="s">
         <v>195</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5291,23 +5284,23 @@
         <v>22</v>
       </c>
       <c r="B24" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>197</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>198</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="G24" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="H24" s="19" t="s">
         <v>201</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>202</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>1</v>
@@ -5325,23 +5318,23 @@
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>203</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>204</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="G25" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="H25" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>208</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>1</v>
@@ -5359,25 +5352,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="F26" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="G26" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="H26" s="19" t="s">
         <v>214</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>215</v>
       </c>
       <c r="I26" s="19" t="n">
         <v>2</v>
@@ -5395,23 +5388,23 @@
         <v>22</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>216</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>217</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F27" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="G27" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="H27" s="19" t="s">
         <v>220</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>221</v>
       </c>
       <c r="I27" s="19" t="n">
         <v>1</v>
@@ -5429,23 +5422,23 @@
         <v>22</v>
       </c>
       <c r="B28" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="G28" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="H28" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="I28" s="19" t="n">
         <v>1</v>
@@ -5463,23 +5456,23 @@
         <v>22</v>
       </c>
       <c r="B29" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>228</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="G29" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="H29" s="19" t="s">
         <v>231</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>232</v>
       </c>
       <c r="I29" s="19" t="n">
         <v>1</v>
@@ -5497,23 +5490,23 @@
         <v>23</v>
       </c>
       <c r="B30" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>233</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>234</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="G30" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="H30" s="19" t="s">
         <v>237</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>238</v>
       </c>
       <c r="I30" s="19" t="n">
         <v>2</v>
@@ -5522,10 +5515,10 @@
         <v>6</v>
       </c>
       <c r="K30" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="L30" s="19" t="s">
         <v>239</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5533,23 +5526,23 @@
         <v>23</v>
       </c>
       <c r="B31" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>241</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>242</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="G31" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="H31" s="19" t="s">
         <v>245</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>246</v>
       </c>
       <c r="I31" s="19" t="n">
         <v>6</v>
@@ -5567,23 +5560,23 @@
         <v>23</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>247</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>248</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="G32" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="H32" s="19" t="s">
         <v>251</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>252</v>
       </c>
       <c r="I32" s="19" t="n">
         <v>2</v>
@@ -5601,23 +5594,23 @@
         <v>23</v>
       </c>
       <c r="B33" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>253</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>254</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="G33" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="H33" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="I33" s="19" t="n">
         <v>2</v>
@@ -5635,23 +5628,23 @@
         <v>23</v>
       </c>
       <c r="B34" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>259</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>260</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="G34" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="H34" s="19" t="s">
         <v>263</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>264</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>1</v>
@@ -5669,23 +5662,23 @@
         <v>23</v>
       </c>
       <c r="B35" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>265</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>266</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="F35" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="G35" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="H35" s="19" t="s">
         <v>269</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>270</v>
       </c>
       <c r="I35" s="19" t="n">
         <v>12</v>
@@ -5694,10 +5687,10 @@
         <v>8</v>
       </c>
       <c r="K35" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="L35" s="19" t="s">
         <v>271</v>
-      </c>
-      <c r="L35" s="19" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5705,23 +5698,23 @@
         <v>23</v>
       </c>
       <c r="B36" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>273</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>274</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="F36" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="G36" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="H36" s="19" t="s">
         <v>277</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>278</v>
       </c>
       <c r="I36" s="19" t="n">
         <v>2</v>
@@ -5739,23 +5732,23 @@
         <v>23</v>
       </c>
       <c r="B37" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>279</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>280</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="G37" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="H37" s="19" t="s">
         <v>283</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>284</v>
       </c>
       <c r="I37" s="19" t="n">
         <v>4</v>
@@ -5764,10 +5757,10 @@
         <v>6</v>
       </c>
       <c r="K37" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="L37" s="19" t="s">
         <v>285</v>
-      </c>
-      <c r="L37" s="19" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5775,23 +5768,23 @@
         <v>24</v>
       </c>
       <c r="B38" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>287</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>288</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="F38" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="G38" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="H38" s="19" t="s">
         <v>291</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>292</v>
       </c>
       <c r="I38" s="19" t="n">
         <v>2</v>
@@ -5809,23 +5802,23 @@
         <v>24</v>
       </c>
       <c r="B39" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>293</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>294</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="G39" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="H39" s="19" t="s">
         <v>297</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>298</v>
       </c>
       <c r="I39" s="19" t="n">
         <v>2</v>
@@ -5843,23 +5836,23 @@
         <v>24</v>
       </c>
       <c r="B40" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>299</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>300</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="G40" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="H40" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="I40" s="19" t="n">
         <v>1</v>
@@ -5877,23 +5870,23 @@
         <v>24</v>
       </c>
       <c r="B41" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>305</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>306</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="G41" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="G41" s="19" t="s">
-        <v>309</v>
-      </c>
       <c r="H41" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I41" s="19" t="n">
         <v>1</v>
@@ -5911,23 +5904,23 @@
         <v>24</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>310</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>311</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="G42" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="H42" s="19" t="s">
         <v>314</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>315</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>2</v>
@@ -5945,23 +5938,23 @@
         <v>24</v>
       </c>
       <c r="B43" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>316</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>317</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="F43" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="G43" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="H43" s="19" t="s">
         <v>320</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>321</v>
       </c>
       <c r="I43" s="19" t="n">
         <v>1</v>
@@ -5979,23 +5972,23 @@
         <v>24</v>
       </c>
       <c r="B44" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>322</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>323</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="F44" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="G44" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="G44" s="19" t="s">
+      <c r="H44" s="19" t="s">
         <v>326</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>327</v>
       </c>
       <c r="I44" s="19" t="n">
         <v>5</v>
@@ -6013,23 +6006,23 @@
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>328</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>329</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="G45" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="H45" s="19" t="s">
         <v>332</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>333</v>
       </c>
       <c r="I45" s="19" t="n">
         <v>1</v>
@@ -6047,23 +6040,23 @@
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="C46" s="19" t="s">
         <v>334</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>335</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="F46" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="G46" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="H46" s="19" t="s">
         <v>337</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>338</v>
       </c>
       <c r="I46" s="19" t="n">
         <v>2</v>
@@ -6081,23 +6074,23 @@
         <v>25</v>
       </c>
       <c r="B47" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="C47" s="19" t="s">
         <v>339</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>340</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="F47" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="G47" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="G47" s="19" t="s">
+      <c r="H47" s="19" t="s">
         <v>343</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>344</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>2</v>
@@ -6106,10 +6099,10 @@
         <v>6</v>
       </c>
       <c r="K47" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="L47" s="19" t="s">
         <v>345</v>
-      </c>
-      <c r="L47" s="19" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6117,23 +6110,23 @@
         <v>25</v>
       </c>
       <c r="B48" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>347</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>348</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="F48" s="19" t="s">
-        <v>350</v>
-      </c>
       <c r="G48" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="H48" s="19" t="s">
         <v>332</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>333</v>
       </c>
       <c r="I48" s="19" t="n">
         <v>1</v>
@@ -6151,23 +6144,23 @@
         <v>26</v>
       </c>
       <c r="B49" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>351</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>352</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="F49" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="G49" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="H49" s="19" t="s">
         <v>355</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>356</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>2</v>
@@ -6185,23 +6178,23 @@
         <v>27</v>
       </c>
       <c r="B50" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="C50" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>358</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F50" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="G50" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="H50" s="19" t="s">
         <v>361</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>362</v>
       </c>
       <c r="I50" s="19" t="n">
         <v>1</v>
@@ -6219,23 +6212,23 @@
         <v>27</v>
       </c>
       <c r="B51" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>363</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>364</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F51" s="19" t="s">
         <v>365</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="G51" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="H51" s="19" t="s">
         <v>367</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>368</v>
       </c>
       <c r="I51" s="19" t="n">
         <v>4</v>
@@ -6244,10 +6237,10 @@
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="L51" s="19" t="s">
         <v>369</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6255,23 +6248,23 @@
         <v>27</v>
       </c>
       <c r="B52" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>371</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>372</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F52" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="F52" s="19" t="s">
+      <c r="G52" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="G52" s="19" t="s">
+      <c r="H52" s="19" t="s">
         <v>375</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>376</v>
       </c>
       <c r="I52" s="19" t="n">
         <v>2</v>
@@ -6289,23 +6282,23 @@
         <v>27</v>
       </c>
       <c r="B53" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="F53" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="F53" s="19" t="s">
+      <c r="G53" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="G53" s="19" t="s">
+      <c r="H53" s="19" t="s">
         <v>381</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>382</v>
       </c>
       <c r="I53" s="19" t="n">
         <v>2</v>
@@ -6323,23 +6316,23 @@
         <v>27</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="F54" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="G54" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="G54" s="19" t="s">
-        <v>386</v>
-      </c>
       <c r="H54" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I54" s="19" t="n">
         <v>2</v>
@@ -6348,10 +6341,10 @@
         <v>6</v>
       </c>
       <c r="K54" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="L54" s="19" t="s">
         <v>387</v>
-      </c>
-      <c r="L54" s="19" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6359,23 +6352,23 @@
         <v>27</v>
       </c>
       <c r="B55" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>389</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>390</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="F55" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="G55" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="G55" s="19" t="s">
-        <v>393</v>
-      </c>
       <c r="H55" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I55" s="19" t="n">
         <v>1</v>
@@ -6393,23 +6386,23 @@
         <v>27</v>
       </c>
       <c r="B56" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>394</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>395</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="F56" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="G56" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="G56" s="19" t="s">
+      <c r="H56" s="19" t="s">
         <v>398</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>399</v>
       </c>
       <c r="I56" s="19" t="n">
         <v>2</v>
@@ -6427,23 +6420,23 @@
         <v>27</v>
       </c>
       <c r="B57" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>400</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>401</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="F57" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="G57" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="G57" s="19" t="s">
+      <c r="H57" s="19" t="s">
         <v>404</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>405</v>
       </c>
       <c r="I57" s="19" t="n">
         <v>2</v>
@@ -6452,10 +6445,10 @@
         <v>6</v>
       </c>
       <c r="K57" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="L57" s="19" t="s">
         <v>406</v>
-      </c>
-      <c r="L57" s="19" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6463,23 +6456,23 @@
         <v>27</v>
       </c>
       <c r="B58" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="C58" s="19" t="s">
         <v>408</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>409</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="F58" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="F58" s="19" t="s">
+      <c r="G58" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="G58" s="19" t="s">
+      <c r="H58" s="19" t="s">
         <v>412</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>413</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>2</v>
@@ -6488,10 +6481,10 @@
         <v>6</v>
       </c>
       <c r="K58" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="L58" s="19" t="s">
         <v>414</v>
-      </c>
-      <c r="L58" s="19" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6499,23 +6492,23 @@
         <v>28</v>
       </c>
       <c r="B59" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="C59" s="19" t="s">
         <v>416</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>417</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="F59" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="F59" s="19" t="s">
+      <c r="G59" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="H59" s="19" t="s">
         <v>419</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>420</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>1</v>
@@ -6524,10 +6517,10 @@
         <v>7</v>
       </c>
       <c r="K59" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="L59" s="19" t="s">
         <v>421</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,23 +6528,23 @@
         <v>29</v>
       </c>
       <c r="B60" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>423</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>424</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="F60" s="19" t="s">
         <v>425</v>
       </c>
-      <c r="F60" s="19" t="s">
+      <c r="G60" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="G60" s="19" t="s">
+      <c r="H60" s="19" t="s">
         <v>427</v>
-      </c>
-      <c r="H60" s="19" t="s">
-        <v>428</v>
       </c>
       <c r="I60" s="19" t="n">
         <v>1</v>
@@ -6569,23 +6562,23 @@
         <v>29</v>
       </c>
       <c r="B61" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>429</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>430</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="F61" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="G61" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="H61" s="19" t="s">
         <v>432</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>433</v>
       </c>
       <c r="I61" s="19" t="n">
         <v>5</v>
@@ -6603,23 +6596,23 @@
         <v>29</v>
       </c>
       <c r="B62" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C62" s="19" t="s">
         <v>434</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>435</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="F62" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="G62" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="H62" s="19" t="s">
         <v>438</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>439</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>1</v>
@@ -6637,23 +6630,23 @@
         <v>29</v>
       </c>
       <c r="B63" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="C63" s="19" t="s">
         <v>440</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>441</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="F63" s="19" t="s">
         <v>442</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="G63" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="G63" s="19" t="s">
-        <v>444</v>
-      </c>
       <c r="H63" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>1</v>
@@ -6671,23 +6664,23 @@
         <v>29</v>
       </c>
       <c r="B64" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>445</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>446</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="F64" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="G64" s="19" t="s">
         <v>448</v>
       </c>
-      <c r="G64" s="19" t="s">
-        <v>449</v>
-      </c>
       <c r="H64" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>1</v>
@@ -6705,23 +6698,23 @@
         <v>29</v>
       </c>
       <c r="B65" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>450</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>451</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="F65" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="G65" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="G65" s="19" t="s">
+      <c r="H65" s="19" t="s">
         <v>454</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>455</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>2</v>
@@ -6730,10 +6723,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="L65" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="L65" s="19" t="s">
-        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6785,25 +6778,25 @@
         <v>40</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>460</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>461</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>462</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6811,19 +6804,19 @@
         <v>137</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>467</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>468</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
@@ -6837,22 +6830,22 @@
         <v>179</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>469</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>472</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>473</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>187</v>
@@ -6863,51 +6856,51 @@
         <v>188</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>474</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>476</v>
-      </c>
       <c r="F4" s="19" t="s">
-        <v>477</v>
+        <v>185</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>480</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -6940,22 +6933,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>486</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6963,16 +6956,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>490</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>492</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6981,16 +6974,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>494</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>495</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>496</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6999,13 +6992,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>497</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>499</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>193</v>
@@ -7017,16 +7010,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>502</v>
-      </c>
       <c r="E5" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F5" s="21"/>
     </row>
@@ -7035,16 +7028,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>504</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>506</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -7053,16 +7046,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>508</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>510</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -7071,16 +7064,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>512</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>514</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -7089,16 +7082,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>515</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="E9" s="19" t="s">
         <v>516</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>518</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -7107,16 +7100,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>519</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>521</v>
-      </c>
       <c r="E10" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -7125,16 +7118,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="19" t="s">
         <v>523</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>525</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7143,16 +7136,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>526</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="E12" s="19" t="s">
         <v>527</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>528</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>529</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -7161,16 +7154,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="E13" s="19" t="s">
         <v>531</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>533</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7179,16 +7172,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>534</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>535</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>537</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7197,13 +7190,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>538</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>540</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>122</v>
@@ -7215,16 +7208,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>541</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="E16" s="19" t="s">
         <v>542</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>544</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7233,16 +7226,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>545</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="E17" s="19" t="s">
         <v>546</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>547</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>548</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7251,16 +7244,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>549</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>551</v>
-      </c>
       <c r="E18" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7269,16 +7262,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>552</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="E19" s="19" t="s">
         <v>553</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>554</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>555</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7312,33 +7305,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>557</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>558</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>559</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>562</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>564</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>80</v>
@@ -7347,18 +7340,18 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>566</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>567</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>568</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>132</v>
@@ -7367,18 +7360,18 @@
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7387,18 +7380,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7407,18 +7400,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7427,18 +7420,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7447,18 +7440,18 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>138</v>
@@ -7467,18 +7460,18 @@
         <v>7</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7487,18 +7480,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7507,18 +7500,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7527,18 +7520,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7547,18 +7540,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7567,18 +7560,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7587,18 +7580,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7607,18 +7600,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7627,18 +7620,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7647,18 +7640,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7667,18 +7660,18 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>615</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>616</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>617</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>625</v>
@@ -7687,18 +7680,18 @@
         <v>52</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D20" s="19" t="n">
         <v>733</v>
@@ -7707,18 +7700,18 @@
         <v>69</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>270</v>
@@ -7727,18 +7720,18 @@
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>37</v>
@@ -7750,13 +7743,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>140</v>
@@ -7765,18 +7758,18 @@
         <v>17</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D24" s="19" t="n">
         <v>120</v>
@@ -7785,18 +7778,18 @@
         <v>6</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>128</v>
@@ -7805,18 +7798,18 @@
         <v>14</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D26" s="19" t="n">
         <v>45</v>
@@ -7828,13 +7821,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D27" s="19" t="n">
         <v>227</v>
@@ -7843,18 +7836,18 @@
         <v>12</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>93</v>
@@ -7863,18 +7856,18 @@
         <v>2</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>35</v>
@@ -7883,18 +7876,18 @@
         <v>3</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>53</v>
@@ -7903,18 +7896,18 @@
         <v>5</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>59</v>
@@ -7923,18 +7916,18 @@
         <v>8</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>54</v>
@@ -7943,18 +7936,18 @@
         <v>7</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>49</v>
@@ -7966,13 +7959,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D34" s="19" t="n">
         <v>204</v>
@@ -7981,18 +7974,18 @@
         <v>14</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
+        <v>659</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>660</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>661</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>662</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>663</v>
       </c>
       <c r="D35" s="19" t="n">
         <v>185</v>
@@ -8001,18 +7994,18 @@
         <v>10</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>593</v>
@@ -8021,18 +8014,18 @@
         <v>36</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D37" s="19" t="n">
         <v>43</v>
@@ -8044,13 +8037,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>31</v>
@@ -8062,13 +8055,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
+        <v>670</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>671</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>672</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>673</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>674</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>192</v>
@@ -8077,18 +8070,18 @@
         <v>7</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>676</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>678</v>
       </c>
       <c r="D40" s="19" t="n">
         <v>60</v>
@@ -8097,18 +8090,18 @@
         <v>9</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>129</v>
@@ -8117,18 +8110,18 @@
         <v>10</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>183</v>
@@ -8137,18 +8130,18 @@
         <v>13</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>17</v>
@@ -8157,18 +8150,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>105</v>
@@ -8177,18 +8170,18 @@
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>691</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>692</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>693</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>34</v>
@@ -8197,18 +8190,18 @@
         <v>1</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>90</v>
@@ -8217,18 +8210,18 @@
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D47" s="19" t="n">
         <v>101</v>
@@ -8237,18 +8230,18 @@
         <v>6</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D48" s="19" t="n">
         <v>55</v>
@@ -8257,7 +8250,7 @@
         <v>3</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -8290,2404 +8283,2404 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>702</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>703</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>704</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>705</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>706</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>707</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>708</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>710</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>711</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>724</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>725</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>726</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>731</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>732</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>733</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>734</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>738</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>739</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>741</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>742</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
+        <v>742</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>744</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="E19" s="19" t="s">
         <v>746</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>747</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>748</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>749</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>750</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C22" s="19" t="s">
+        <v>752</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>753</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>754</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>755</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C23" s="19" t="s">
+        <v>755</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>756</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>757</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>758</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C24" s="19" t="s">
+        <v>758</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>759</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>760</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>761</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C25" s="19" t="s">
+        <v>761</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>763</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>764</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C26" s="19" t="s">
+        <v>764</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>765</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>766</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>767</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C27" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>769</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>770</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C28" s="19" t="s">
+        <v>770</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="E28" s="19" t="s">
         <v>772</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
+        <v>773</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>775</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="D29" s="19" t="s">
         <v>776</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="E29" s="19" t="s">
         <v>777</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>778</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C31" s="19" t="s">
+        <v>780</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>782</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>783</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C33" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="E33" s="19" t="s">
         <v>786</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>787</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C34" s="19" t="s">
+        <v>787</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>789</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>790</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C35" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>792</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>793</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C44" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="E44" s="19" t="s">
         <v>809</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>810</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B45" s="19" t="s">
+        <v>810</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="D45" s="19" t="s">
         <v>812</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>813</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>814</v>
-      </c>
       <c r="E45" s="19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
+        <v>819</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>820</v>
+      </c>
+      <c r="C50" s="19" t="s">
         <v>821</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="D50" s="19" t="s">
         <v>822</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="E50" s="19" t="s">
         <v>823</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>824</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B51" s="19" t="s">
+        <v>824</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="D51" s="19" t="s">
         <v>826</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="E51" s="19" t="s">
         <v>827</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>828</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C52" s="19" t="s">
+        <v>828</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>830</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>831</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C53" s="19" t="s">
+        <v>831</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>832</v>
+      </c>
+      <c r="E53" s="19" t="s">
         <v>833</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>834</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C54" s="19" t="s">
+        <v>834</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>835</v>
+      </c>
+      <c r="E54" s="19" t="s">
         <v>836</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>837</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C56" s="19" t="s">
+        <v>839</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="E56" s="19" t="s">
         <v>841</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>842</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C57" s="19" t="s">
+        <v>842</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>843</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>844</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>845</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C58" s="19" t="s">
+        <v>845</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>846</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>847</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>848</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C59" s="19" t="s">
+        <v>848</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>849</v>
+      </c>
+      <c r="E59" s="19" t="s">
         <v>850</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>851</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C61" s="19" t="s">
+        <v>853</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>854</v>
+      </c>
+      <c r="E61" s="19" t="s">
         <v>855</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>856</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C62" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>857</v>
+      </c>
+      <c r="E62" s="19" t="s">
         <v>858</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>859</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C63" s="19" t="s">
+        <v>859</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>860</v>
+      </c>
+      <c r="E63" s="19" t="s">
         <v>861</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>862</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C64" s="19" t="s">
+        <v>862</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>863</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>864</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>865</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C65" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>866</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>867</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>868</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C66" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>869</v>
+      </c>
+      <c r="E66" s="19" t="s">
         <v>870</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>871</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C67" s="19" t="s">
+        <v>871</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>872</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>873</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>874</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C68" s="19" t="s">
+        <v>874</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>876</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>877</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C69" s="19" t="s">
+        <v>877</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="E69" s="19" t="s">
         <v>879</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>880</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C70" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>881</v>
+      </c>
+      <c r="E70" s="19" t="s">
         <v>882</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>883</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
+        <v>883</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>884</v>
+      </c>
+      <c r="C71" s="19" t="s">
         <v>885</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="D71" s="19" t="s">
         <v>886</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="E71" s="19" t="s">
         <v>887</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>888</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C72" s="19" t="s">
+        <v>888</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>889</v>
+      </c>
+      <c r="E72" s="19" t="s">
         <v>890</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>891</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D73" s="19"/>
       <c r="E73" s="19" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C74" s="19" t="s">
+        <v>892</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>893</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>894</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>895</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D75" s="19"/>
       <c r="E75" s="19" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C76" s="19" t="s">
+        <v>897</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>898</v>
+      </c>
+      <c r="E76" s="19" t="s">
         <v>899</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>900</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C77" s="19" t="s">
+        <v>900</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>901</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>902</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>903</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B78" s="19" t="s">
+        <v>903</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>904</v>
+      </c>
+      <c r="D78" s="19" t="s">
         <v>905</v>
       </c>
-      <c r="C78" s="19" t="s">
+      <c r="E78" s="19" t="s">
         <v>906</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>907</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C80" s="19" t="s">
+        <v>909</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>910</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>911</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>912</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C81" s="19" t="s">
+        <v>912</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>913</v>
+      </c>
+      <c r="E81" s="19" t="s">
         <v>914</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>915</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C82" s="19" t="s">
+        <v>915</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>916</v>
+      </c>
+      <c r="E82" s="19" t="s">
         <v>917</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>918</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C83" s="19" t="s">
+        <v>918</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>919</v>
+      </c>
+      <c r="E83" s="19" t="s">
         <v>920</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>921</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C84" s="19" t="s">
+        <v>921</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>922</v>
+      </c>
+      <c r="E84" s="19" t="s">
         <v>923</v>
-      </c>
-      <c r="D84" s="19" t="s">
-        <v>924</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C85" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>925</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>926</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>927</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
+        <v>927</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>928</v>
+      </c>
+      <c r="C86" s="19" t="s">
         <v>929</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="D86" s="19" t="s">
         <v>930</v>
       </c>
-      <c r="C86" s="19" t="s">
+      <c r="E86" s="19" t="s">
         <v>931</v>
-      </c>
-      <c r="D86" s="19" t="s">
-        <v>932</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D87" s="19"/>
       <c r="E87" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D93" s="19"/>
       <c r="E93" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D100" s="19"/>
       <c r="E100" s="19" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C101" s="19" t="s">
+        <v>952</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>953</v>
+      </c>
+      <c r="E101" s="19" t="s">
         <v>954</v>
-      </c>
-      <c r="D101" s="19" t="s">
-        <v>955</v>
-      </c>
-      <c r="E101" s="19" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D104" s="19"/>
       <c r="E104" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D105" s="19"/>
       <c r="E105" s="19" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D107" s="19"/>
       <c r="E107" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C108" s="19" t="s">
+        <v>966</v>
+      </c>
+      <c r="D108" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="E108" s="19" t="s">
         <v>968</v>
-      </c>
-      <c r="D108" s="19" t="s">
-        <v>969</v>
-      </c>
-      <c r="E108" s="19" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C110" s="19" t="s">
+        <v>971</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="E110" s="19" t="s">
         <v>973</v>
-      </c>
-      <c r="D110" s="19" t="s">
-        <v>974</v>
-      </c>
-      <c r="E110" s="19" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D111" s="19"/>
       <c r="E111" s="19" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
+        <v>987</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>988</v>
+      </c>
+      <c r="C118" s="19" t="s">
         <v>989</v>
       </c>
-      <c r="B118" s="19" t="s">
+      <c r="D118" s="19" t="s">
         <v>990</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="E118" s="19" t="s">
         <v>991</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>992</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C119" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>993</v>
+      </c>
+      <c r="E119" s="19" t="s">
         <v>994</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>995</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C125" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E125" s="19" t="s">
         <v>1007</v>
-      </c>
-      <c r="D125" s="19" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E125" s="19" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D126" s="19"/>
       <c r="E126" s="19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D128" s="19"/>
       <c r="E128" s="19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C130" s="19" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E130" s="19" t="s">
         <v>1017</v>
-      </c>
-      <c r="D130" s="19" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E130" s="19" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="D131" s="19"/>
       <c r="E131" s="19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C132" s="19" t="s">
         <v>1021</v>
-      </c>
-      <c r="B132" s="19" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C132" s="19" t="s">
-        <v>1023</v>
       </c>
       <c r="D132" s="19"/>
       <c r="E132" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C134" s="19" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E134" s="19" t="s">
         <v>1027</v>
-      </c>
-      <c r="D134" s="19" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E134" s="19" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C135" s="19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E135" s="19" t="s">
         <v>1030</v>
-      </c>
-      <c r="D135" s="19" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E135" s="19" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B136" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D136" s="19" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E136" s="19" t="s">
         <v>1022</v>
-      </c>
-      <c r="C136" s="19" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D136" s="19" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E136" s="19" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D139" s="19"/>
       <c r="E139" s="19" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D142" s="19"/>
       <c r="E142" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D143" s="19"/>
       <c r="E143" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D144" s="19"/>
       <c r="E144" s="19" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B145" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D145" s="19"/>
       <c r="E145" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="19" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B146" s="19" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D146" s="19"/>
       <c r="E146" s="19" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
   </sheetData>

--- a/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Recapitulatif_requis_VISU_PTBG.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1049">
   <si>
     <t xml:space="preserve">Récapitulatif des requis — VISU PTBG 1.0.0</t>
   </si>
@@ -150,10 +150,16 @@
     <t xml:space="preserve">Vérifications faites le 28/10/2026 : 64 lignes du Word toutes présentes dans la matrice, chaque requis cité dans le code et dans au moins un test</t>
   </si>
   <si>
-    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe. Les 145 tests sont à lancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sur le poste Windows et sur la VM Linux. Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
+    <t xml:space="preserve">(tools/verifier_tracabilite.py : « Traçabilité complète ») ; chaque fichier, fonction et test cité ici existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests lancés sur le PC Windows 11 / Spyder 6 le 30/10/2026 : 144 sur 145 OK (le dernier cherchait le Word de la spécification, absent du dossier ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corrigé : ce test est sauté sans le Word). Reste à les lancer sur la VM Linux SLES 15 SP7 fournie par l'entreprise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonne jaune « Réponse de Sébastien » de l'onglet Points ouverts : à remplir lors de la revue.</t>
   </si>
   <si>
     <t xml:space="preserve">Section du Word</t>
@@ -1523,7 +1529,7 @@
     <t xml:space="preserve">ptbg/system/compat.py ; install/ ; docs/COMPATIBILITE_OS.md</t>
   </si>
   <si>
-    <t xml:space="preserve">test_architecture.test_os_specific_code_is_centralized ; essais à faire sur le poste Windows et la VM Linux SLES fournie par l'entreprise</t>
+    <t xml:space="preserve">test_architecture.test_os_specific_code_is_centralized ; tests lancés sur le PC Windows 11 / Spyder 6 le 30/10/2026 (144 sur 145 OK, le dernier cherchait le Word de la spécification, absent ; corrigé) ; essai de réception à faire sur le PC, tests et essai à faire sur la VM Linux SLES fournie par l'entreprise</t>
   </si>
   <si>
     <t xml:space="preserve">Qualification sur cible à faire</t>
@@ -2423,7 +2429,7 @@
     <t xml:space="preserve">test_every_requirement_is_traced</t>
   </si>
   <si>
-    <t xml:space="preserve">Aucun requis du Word laissé de côté : matrice + code + test.</t>
+    <t xml:space="preserve">Aucun requis du Word laissé de côté : matrice + code + test. Le Word de la</t>
   </si>
   <si>
     <t xml:space="preserve">module : 3001</t>
@@ -3902,7 +3908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -4436,6 +4442,16 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4473,40 +4489,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L1" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4514,23 +4530,23 @@
         <v>19</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I2" s="19" t="n">
         <v>1</v>
@@ -4548,23 +4564,23 @@
         <v>19</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I3" s="19" t="n">
         <v>1</v>
@@ -4582,23 +4598,23 @@
         <v>19</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I4" s="19" t="n">
         <v>2</v>
@@ -4616,23 +4632,23 @@
         <v>19</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="19" t="n">
         <v>1</v>
@@ -4650,23 +4666,23 @@
         <v>19</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>4</v>
@@ -4684,23 +4700,23 @@
         <v>19</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>2</v>
@@ -4718,23 +4734,23 @@
         <v>20</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>2</v>
@@ -4752,23 +4768,23 @@
         <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>1</v>
@@ -4780,7 +4796,7 @@
         <v>5</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4788,23 +4804,23 @@
         <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>2</v>
@@ -4813,10 +4829,10 @@
         <v>6</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4824,23 +4840,23 @@
         <v>21</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>1</v>
@@ -4858,23 +4874,23 @@
         <v>21</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>5</v>
@@ -4886,7 +4902,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4894,23 +4910,23 @@
         <v>21</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>4</v>
@@ -4919,7 +4935,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L13" s="19"/>
     </row>
@@ -4928,23 +4944,23 @@
         <v>21</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I14" s="19" t="n">
         <v>2</v>
@@ -4962,23 +4978,23 @@
         <v>21</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I15" s="19" t="n">
         <v>1</v>
@@ -4996,25 +5012,25 @@
         <v>21</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I16" s="19" t="n">
         <v>2</v>
@@ -5023,10 +5039,10 @@
         <v>6</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5034,23 +5050,23 @@
         <v>21</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I17" s="19" t="n">
         <v>3</v>
@@ -5068,23 +5084,23 @@
         <v>21</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I18" s="19" t="n">
         <v>6</v>
@@ -5093,10 +5109,10 @@
         <v>6</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5104,23 +5120,23 @@
         <v>21</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I19" s="19" t="n">
         <v>3</v>
@@ -5138,23 +5154,23 @@
         <v>21</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I20" s="19" t="n">
         <v>1</v>
@@ -5172,23 +5188,23 @@
         <v>21</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I21" s="19" t="n">
         <v>1</v>
@@ -5197,10 +5213,10 @@
         <v>6</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5208,25 +5224,25 @@
         <v>22</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I22" s="19" t="n">
         <v>1</v>
@@ -5235,10 +5251,10 @@
         <v>8</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5246,25 +5262,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>1</v>
@@ -5273,10 +5289,10 @@
         <v>6</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5284,23 +5300,23 @@
         <v>22</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>1</v>
@@ -5318,23 +5334,23 @@
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>1</v>
@@ -5352,25 +5368,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I26" s="19" t="n">
         <v>2</v>
@@ -5388,23 +5404,23 @@
         <v>22</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I27" s="19" t="n">
         <v>1</v>
@@ -5422,23 +5438,23 @@
         <v>22</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I28" s="19" t="n">
         <v>1</v>
@@ -5456,23 +5472,23 @@
         <v>22</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I29" s="19" t="n">
         <v>1</v>
@@ -5490,23 +5506,23 @@
         <v>23</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I30" s="19" t="n">
         <v>2</v>
@@ -5515,10 +5531,10 @@
         <v>6</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L30" s="19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5526,23 +5542,23 @@
         <v>23</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I31" s="19" t="n">
         <v>6</v>
@@ -5560,23 +5576,23 @@
         <v>23</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I32" s="19" t="n">
         <v>2</v>
@@ -5594,23 +5610,23 @@
         <v>23</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I33" s="19" t="n">
         <v>2</v>
@@ -5628,23 +5644,23 @@
         <v>23</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>1</v>
@@ -5662,23 +5678,23 @@
         <v>23</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I35" s="19" t="n">
         <v>12</v>
@@ -5687,10 +5703,10 @@
         <v>8</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5698,23 +5714,23 @@
         <v>23</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I36" s="19" t="n">
         <v>2</v>
@@ -5732,23 +5748,23 @@
         <v>23</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I37" s="19" t="n">
         <v>4</v>
@@ -5757,10 +5773,10 @@
         <v>6</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L37" s="19" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,23 +5784,23 @@
         <v>24</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I38" s="19" t="n">
         <v>2</v>
@@ -5802,23 +5818,23 @@
         <v>24</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I39" s="19" t="n">
         <v>2</v>
@@ -5836,23 +5852,23 @@
         <v>24</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I40" s="19" t="n">
         <v>1</v>
@@ -5870,23 +5886,23 @@
         <v>24</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I41" s="19" t="n">
         <v>1</v>
@@ -5904,23 +5920,23 @@
         <v>24</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>2</v>
@@ -5938,23 +5954,23 @@
         <v>24</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I43" s="19" t="n">
         <v>1</v>
@@ -5972,23 +5988,23 @@
         <v>24</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I44" s="19" t="n">
         <v>5</v>
@@ -6006,23 +6022,23 @@
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I45" s="19" t="n">
         <v>1</v>
@@ -6040,23 +6056,23 @@
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I46" s="19" t="n">
         <v>2</v>
@@ -6074,23 +6090,23 @@
         <v>25</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>2</v>
@@ -6099,10 +6115,10 @@
         <v>6</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6110,23 +6126,23 @@
         <v>25</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I48" s="19" t="n">
         <v>1</v>
@@ -6144,23 +6160,23 @@
         <v>26</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>2</v>
@@ -6178,23 +6194,23 @@
         <v>27</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I50" s="19" t="n">
         <v>1</v>
@@ -6212,23 +6228,23 @@
         <v>27</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I51" s="19" t="n">
         <v>4</v>
@@ -6237,10 +6253,10 @@
         <v>6</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,23 +6264,23 @@
         <v>27</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I52" s="19" t="n">
         <v>2</v>
@@ -6282,23 +6298,23 @@
         <v>27</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I53" s="19" t="n">
         <v>2</v>
@@ -6316,23 +6332,23 @@
         <v>27</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="H54" s="19" t="s">
         <v>383</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>381</v>
       </c>
       <c r="I54" s="19" t="n">
         <v>2</v>
@@ -6341,10 +6357,10 @@
         <v>6</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6352,23 +6368,23 @@
         <v>27</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I55" s="19" t="n">
         <v>1</v>
@@ -6386,23 +6402,23 @@
         <v>27</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I56" s="19" t="n">
         <v>2</v>
@@ -6420,23 +6436,23 @@
         <v>27</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I57" s="19" t="n">
         <v>2</v>
@@ -6445,10 +6461,10 @@
         <v>6</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6456,23 +6472,23 @@
         <v>27</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I58" s="19" t="n">
         <v>2</v>
@@ -6481,10 +6497,10 @@
         <v>6</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6492,23 +6508,23 @@
         <v>28</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I59" s="19" t="n">
         <v>1</v>
@@ -6517,10 +6533,10 @@
         <v>7</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6528,23 +6544,23 @@
         <v>29</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I60" s="19" t="n">
         <v>1</v>
@@ -6562,23 +6578,23 @@
         <v>29</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I61" s="19" t="n">
         <v>5</v>
@@ -6596,23 +6612,23 @@
         <v>29</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I62" s="19" t="n">
         <v>1</v>
@@ -6630,23 +6646,23 @@
         <v>29</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="19" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I63" s="19" t="n">
         <v>1</v>
@@ -6664,23 +6680,23 @@
         <v>29</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I64" s="19" t="n">
         <v>1</v>
@@ -6698,23 +6714,23 @@
         <v>29</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I65" s="19" t="n">
         <v>2</v>
@@ -6723,10 +6739,10 @@
         <v>6</v>
       </c>
       <c r="K65" s="19" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -6775,132 +6791,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -6933,22 +6949,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6956,16 +6972,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F2" s="21"/>
     </row>
@@ -6974,16 +6990,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F3" s="21"/>
     </row>
@@ -6992,16 +7008,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F4" s="21"/>
     </row>
@@ -7010,16 +7026,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F5" s="21"/>
     </row>
@@ -7028,16 +7044,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F6" s="21"/>
     </row>
@@ -7046,16 +7062,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F7" s="21"/>
     </row>
@@ -7064,16 +7080,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F8" s="21"/>
     </row>
@@ -7082,16 +7098,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F9" s="21"/>
     </row>
@@ -7100,16 +7116,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F10" s="21"/>
     </row>
@@ -7118,16 +7134,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7136,16 +7152,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F12" s="21"/>
     </row>
@@ -7154,16 +7170,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F13" s="21"/>
     </row>
@@ -7172,16 +7188,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F14" s="21"/>
     </row>
@@ -7190,16 +7206,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F15" s="21"/>
     </row>
@@ -7208,16 +7224,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F16" s="21"/>
     </row>
@@ -7226,16 +7242,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F17" s="21"/>
     </row>
@@ -7244,16 +7260,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F18" s="21"/>
     </row>
@@ -7262,16 +7278,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F19" s="21"/>
     </row>
@@ -7305,33 +7321,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>80</v>
@@ -7340,18 +7356,18 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>132</v>
@@ -7360,18 +7376,18 @@
         <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>111</v>
@@ -7380,18 +7396,18 @@
         <v>12</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>643</v>
@@ -7400,18 +7416,18 @@
         <v>39</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>61</v>
@@ -7420,18 +7436,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>284</v>
@@ -7440,18 +7456,18 @@
         <v>41</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>138</v>
@@ -7460,18 +7476,18 @@
         <v>7</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>32</v>
@@ -7480,18 +7496,18 @@
         <v>5</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>75</v>
@@ -7500,18 +7516,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>116</v>
@@ -7520,18 +7536,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>149</v>
@@ -7540,18 +7556,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>187</v>
@@ -7560,18 +7576,18 @@
         <v>14</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>168</v>
@@ -7580,18 +7596,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>368</v>
@@ -7600,18 +7616,18 @@
         <v>19</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>443</v>
@@ -7620,18 +7636,18 @@
         <v>25</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>129</v>
@@ -7640,18 +7656,18 @@
         <v>4</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>87</v>
@@ -7660,18 +7676,18 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>625</v>
@@ -7680,18 +7696,18 @@
         <v>52</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D20" s="19" t="n">
         <v>733</v>
@@ -7700,18 +7716,18 @@
         <v>69</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>270</v>
@@ -7720,18 +7736,18 @@
         <v>26</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>37</v>
@@ -7743,13 +7759,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>140</v>
@@ -7758,18 +7774,18 @@
         <v>17</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D24" s="19" t="n">
         <v>120</v>
@@ -7778,18 +7794,18 @@
         <v>6</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>128</v>
@@ -7798,18 +7814,18 @@
         <v>14</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D26" s="19" t="n">
         <v>45</v>
@@ -7821,13 +7837,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D27" s="19" t="n">
         <v>227</v>
@@ -7836,18 +7852,18 @@
         <v>12</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>93</v>
@@ -7856,18 +7872,18 @@
         <v>2</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>35</v>
@@ -7876,18 +7892,18 @@
         <v>3</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>53</v>
@@ -7896,18 +7912,18 @@
         <v>5</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>59</v>
@@ -7916,18 +7932,18 @@
         <v>8</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>54</v>
@@ -7936,18 +7952,18 @@
         <v>7</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>49</v>
@@ -7959,13 +7975,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D34" s="19" t="n">
         <v>204</v>
@@ -7974,18 +7990,18 @@
         <v>14</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D35" s="19" t="n">
         <v>185</v>
@@ -7994,18 +8010,18 @@
         <v>10</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>593</v>
@@ -8014,18 +8030,18 @@
         <v>36</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D37" s="19" t="n">
         <v>43</v>
@@ -8037,13 +8053,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>31</v>
@@ -8055,13 +8071,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>192</v>
@@ -8070,18 +8086,18 @@
         <v>7</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D40" s="19" t="n">
         <v>60</v>
@@ -8090,18 +8106,18 @@
         <v>9</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>129</v>
@@ -8110,18 +8126,18 @@
         <v>10</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>183</v>
@@ -8130,18 +8146,18 @@
         <v>13</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>17</v>
@@ -8150,18 +8166,18 @@
         <v>1</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>105</v>
@@ -8170,18 +8186,18 @@
         <v>3</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>34</v>
@@ -8190,18 +8206,18 @@
         <v>1</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>692</v>
       </c>
-      <c r="B46" s="19" t="s">
-        <v>690</v>
-      </c>
       <c r="C46" s="19" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>90</v>
@@ -8210,18 +8226,18 @@
         <v>3</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D47" s="19" t="n">
         <v>101</v>
@@ -8230,27 +8246,27 @@
         <v>6</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D48" s="19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E48" s="19" t="n">
         <v>3</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -8283,2404 +8299,2404 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D4" s="19" t="s">
+        <v>716</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>714</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D73" s="19"/>
       <c r="E73" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D75" s="19"/>
       <c r="E75" s="19" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D87" s="19"/>
       <c r="E87" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C88" s="19" t="s">
+        <v>935</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>936</v>
+      </c>
+      <c r="E88" s="19" t="s">
         <v>933</v>
-      </c>
-      <c r="D88" s="19" t="s">
-        <v>934</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D93" s="19"/>
       <c r="E93" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D100" s="19"/>
       <c r="E100" s="19" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D104" s="19"/>
       <c r="E104" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D105" s="19"/>
       <c r="E105" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D107" s="19"/>
       <c r="E107" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D109" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="E109" s="19" t="s">
         <v>970</v>
-      </c>
-      <c r="E109" s="19" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D111" s="19"/>
       <c r="E111" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D126" s="19"/>
       <c r="E126" s="19" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D128" s="19"/>
       <c r="E128" s="19" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D131" s="19"/>
       <c r="E131" s="19" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D132" s="19"/>
       <c r="E132" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D134" s="19" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E137" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D139" s="19"/>
       <c r="E139" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D142" s="19"/>
       <c r="E142" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D143" s="19"/>
       <c r="E143" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D144" s="19"/>
       <c r="E144" s="19" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B145" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D145" s="19"/>
       <c r="E145" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B146" s="19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D146" s="19"/>
       <c r="E146" s="19" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
